--- a/pricing/starter-catalog-pricing.xlsx
+++ b/pricing/starter-catalog-pricing.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18794" uniqueCount="2504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18834" uniqueCount="2508">
   <si>
     <t>STARTER CATALOG — GENERIC ITEMS. Fill in the YELLOW 'Pack price' column only; 'Price per unit' calculates itself as Pack price / Pack qty. 'NEW' marks a row not yet in the app's catalog. Rows with no NEW flag already exist and keep their exact name, unit and category. Sorted by category, then type, then physical size — so the nine sizes of one part sit together. Filter the Type column to work one part at a time.</t>
   </si>
@@ -6447,6 +6447,9 @@
     <t>Eaton BR 100A 2-Pole breaker</t>
   </si>
   <si>
+    <t>Eaton BR 110A 2-Pole breaker</t>
+  </si>
+  <si>
     <t>Eaton BR 125A 2-Pole breaker</t>
   </si>
   <si>
@@ -6495,6 +6498,9 @@
     <t>Eaton CH 100A 2-Pole breaker</t>
   </si>
   <si>
+    <t>Eaton CH 110A 2-Pole breaker</t>
+  </si>
+  <si>
     <t>Eaton CH 125A 2-Pole breaker</t>
   </si>
   <si>
@@ -6582,6 +6588,9 @@
     <t>Siemens 100A 2-Pole breaker</t>
   </si>
   <si>
+    <t>Siemens 110A 2-Pole breaker</t>
+  </si>
+  <si>
     <t>Siemens 125A 2-Pole breaker</t>
   </si>
   <si>
@@ -6715,6 +6724,9 @@
   </si>
   <si>
     <t>Square D QO 100A 2-Pole breaker</t>
+  </si>
+  <si>
+    <t>Square D QO 110A 2-Pole breaker</t>
   </si>
   <si>
     <t>Square D QO 125A 2-Pole breaker</t>
@@ -36609,8 +36621,8 @@
       <c r="F735" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G735" s="5" t="s">
-        <v>7</v>
+      <c r="G735" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H735" s="3" t="s">
         <v>18</v>
@@ -36687,8 +36699,8 @@
       <c r="F737" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G737" s="5" t="s">
-        <v>7</v>
+      <c r="G737" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H737" s="3" t="s">
         <v>18</v>
@@ -36726,8 +36738,8 @@
       <c r="F738" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G738" s="5" t="s">
-        <v>7</v>
+      <c r="G738" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H738" s="3" t="s">
         <v>18</v>
@@ -36765,8 +36777,8 @@
       <c r="F739" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G739" s="5" t="s">
-        <v>7</v>
+      <c r="G739" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H739" s="3" t="s">
         <v>18</v>
@@ -36804,8 +36816,8 @@
       <c r="F740" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G740" s="5" t="s">
-        <v>7</v>
+      <c r="G740" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H740" s="3" t="s">
         <v>18</v>
@@ -37272,8 +37284,8 @@
       <c r="F752" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G752" s="5" t="s">
-        <v>7</v>
+      <c r="G752" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H752" s="3" t="s">
         <v>18</v>
@@ -37350,8 +37362,8 @@
       <c r="F754" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G754" s="5" t="s">
-        <v>7</v>
+      <c r="G754" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H754" s="3" t="s">
         <v>18</v>
@@ -37428,8 +37440,8 @@
       <c r="F756" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G756" s="5" t="s">
-        <v>7</v>
+      <c r="G756" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H756" s="3" t="s">
         <v>18</v>
@@ -37506,8 +37518,8 @@
       <c r="F758" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G758" s="5" t="s">
-        <v>7</v>
+      <c r="G758" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H758" s="3" t="s">
         <v>18</v>
@@ -37662,8 +37674,8 @@
       <c r="F762" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G762" s="5" t="s">
-        <v>7</v>
+      <c r="G762" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H762" s="3" t="s">
         <v>18</v>
@@ -37701,8 +37713,8 @@
       <c r="F763" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G763" s="5" t="s">
-        <v>7</v>
+      <c r="G763" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H763" s="3" t="s">
         <v>18</v>
@@ -37779,8 +37791,8 @@
       <c r="F765" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G765" s="5" t="s">
-        <v>7</v>
+      <c r="G765" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H765" s="3" t="s">
         <v>18</v>
@@ -37818,8 +37830,8 @@
       <c r="F766" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G766" s="5" t="s">
-        <v>7</v>
+      <c r="G766" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H766" s="3" t="s">
         <v>18</v>
@@ -38364,8 +38376,8 @@
       <c r="F780" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G780" s="5" t="s">
-        <v>7</v>
+      <c r="G780" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H780" s="3" t="s">
         <v>18</v>
@@ -38559,8 +38571,8 @@
       <c r="F785" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G785" s="5" t="s">
-        <v>7</v>
+      <c r="G785" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H785" s="3" t="s">
         <v>18</v>
@@ -38598,8 +38610,8 @@
       <c r="F786" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G786" s="5" t="s">
-        <v>7</v>
+      <c r="G786" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H786" s="3" t="s">
         <v>18</v>
@@ -38637,8 +38649,8 @@
       <c r="F787" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G787" s="5" t="s">
-        <v>7</v>
+      <c r="G787" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H787" s="3" t="s">
         <v>18</v>
@@ -38676,8 +38688,8 @@
       <c r="F788" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G788" s="5" t="s">
-        <v>7</v>
+      <c r="G788" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H788" s="3" t="s">
         <v>18</v>
@@ -38715,8 +38727,8 @@
       <c r="F789" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G789" s="5" t="s">
-        <v>7</v>
+      <c r="G789" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H789" s="3" t="s">
         <v>18</v>
@@ -38754,8 +38766,8 @@
       <c r="F790" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G790" s="5" t="s">
-        <v>7</v>
+      <c r="G790" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H790" s="3" t="s">
         <v>18</v>
@@ -38793,8 +38805,8 @@
       <c r="F791" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G791" s="5" t="s">
-        <v>7</v>
+      <c r="G791" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H791" s="3" t="s">
         <v>18</v>
@@ -38832,8 +38844,8 @@
       <c r="F792" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G792" s="5" t="s">
-        <v>7</v>
+      <c r="G792" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H792" s="3" t="s">
         <v>18</v>
@@ -38871,8 +38883,8 @@
       <c r="F793" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G793" s="5" t="s">
-        <v>7</v>
+      <c r="G793" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H793" s="3" t="s">
         <v>18</v>
@@ -38910,8 +38922,8 @@
       <c r="F794" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G794" s="5" t="s">
-        <v>7</v>
+      <c r="G794" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H794" s="3" t="s">
         <v>18</v>
@@ -38949,8 +38961,8 @@
       <c r="F795" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G795" s="5" t="s">
-        <v>7</v>
+      <c r="G795" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H795" s="3" t="s">
         <v>18</v>
@@ -38988,8 +39000,8 @@
       <c r="F796" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G796" s="5" t="s">
-        <v>7</v>
+      <c r="G796" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H796" s="3" t="s">
         <v>18</v>
@@ -39027,8 +39039,8 @@
       <c r="F797" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G797" s="5" t="s">
-        <v>7</v>
+      <c r="G797" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H797" s="3" t="s">
         <v>18</v>
@@ -39066,8 +39078,8 @@
       <c r="F798" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G798" s="5" t="s">
-        <v>7</v>
+      <c r="G798" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H798" s="3" t="s">
         <v>18</v>
@@ -39105,8 +39117,8 @@
       <c r="F799" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G799" s="5" t="s">
-        <v>7</v>
+      <c r="G799" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H799" s="3" t="s">
         <v>18</v>
@@ -39144,8 +39156,8 @@
       <c r="F800" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G800" s="5" t="s">
-        <v>7</v>
+      <c r="G800" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H800" s="3" t="s">
         <v>18</v>
@@ -61016,7 +61028,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M517"/>
+  <dimension ref="A1:M521"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -68152,7 +68164,7 @@
     </row>
     <row r="184" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B184" s="3" t="s">
         <v>1068</v>
@@ -68164,7 +68176,7 @@
         <v>2144</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>975</v>
+        <v>1127</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>333</v>
@@ -68191,7 +68203,7 @@
     </row>
     <row r="185" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B185" s="3" t="s">
         <v>1068</v>
@@ -68203,7 +68215,7 @@
         <v>2145</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>988</v>
+        <v>975</v>
       </c>
       <c r="F185" s="3" t="s">
         <v>333</v>
@@ -68230,7 +68242,7 @@
     </row>
     <row r="186" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
-        <v>1110</v>
+        <v>1129</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>1068</v>
@@ -68242,7 +68254,7 @@
         <v>2146</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>805</v>
+        <v>988</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>333</v>
@@ -68269,7 +68281,7 @@
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
-        <v>1132</v>
+        <v>1110</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>1068</v>
@@ -68281,7 +68293,7 @@
         <v>2147</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>990</v>
+        <v>805</v>
       </c>
       <c r="F187" s="3" t="s">
         <v>333</v>
@@ -68308,7 +68320,7 @@
     </row>
     <row r="188" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
-        <v>1112</v>
+        <v>1132</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>1068</v>
@@ -68320,7 +68332,7 @@
         <v>2148</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>815</v>
+        <v>990</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>333</v>
@@ -68347,7 +68359,7 @@
     </row>
     <row r="189" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>1068</v>
@@ -68359,7 +68371,7 @@
         <v>2149</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>1087</v>
+        <v>815</v>
       </c>
       <c r="F189" s="3" t="s">
         <v>333</v>
@@ -68386,7 +68398,7 @@
     </row>
     <row r="190" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>1068</v>
@@ -68398,7 +68410,7 @@
         <v>2150</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>810</v>
+        <v>1087</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>333</v>
@@ -68425,7 +68437,7 @@
     </row>
     <row r="191" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>1068</v>
@@ -68437,7 +68449,7 @@
         <v>2151</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>1090</v>
+        <v>810</v>
       </c>
       <c r="F191" s="3" t="s">
         <v>333</v>
@@ -68464,7 +68476,7 @@
     </row>
     <row r="192" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>1068</v>
@@ -68476,7 +68488,7 @@
         <v>2152</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>1075</v>
+        <v>1090</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>333</v>
@@ -68503,7 +68515,7 @@
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>1068</v>
@@ -68515,7 +68527,7 @@
         <v>2153</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>1093</v>
+        <v>1075</v>
       </c>
       <c r="F193" s="3" t="s">
         <v>333</v>
@@ -68542,7 +68554,7 @@
     </row>
     <row r="194" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>1068</v>
@@ -68554,7 +68566,7 @@
         <v>2154</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>837</v>
+        <v>1093</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>333</v>
@@ -68581,7 +68593,7 @@
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>1068</v>
@@ -68593,7 +68605,7 @@
         <v>2155</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>966</v>
+        <v>837</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>333</v>
@@ -68620,7 +68632,7 @@
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>1068</v>
@@ -68632,7 +68644,7 @@
         <v>2156</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>1097</v>
+        <v>966</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>333</v>
@@ -68659,7 +68671,7 @@
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="B197" s="3" t="s">
         <v>1068</v>
@@ -68671,7 +68683,7 @@
         <v>2157</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>1122</v>
+        <v>1097</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>333</v>
@@ -68698,7 +68710,7 @@
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>1068</v>
@@ -68710,7 +68722,7 @@
         <v>2158</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>333</v>
@@ -68737,7 +68749,7 @@
     </row>
     <row r="199" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>1068</v>
@@ -68749,7 +68761,7 @@
         <v>2159</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>968</v>
+        <v>1124</v>
       </c>
       <c r="F199" s="3" t="s">
         <v>333</v>
@@ -68776,7 +68788,7 @@
     </row>
     <row r="200" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>1068</v>
@@ -68788,7 +68800,7 @@
         <v>2160</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>975</v>
+        <v>968</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>333</v>
@@ -68815,7 +68827,7 @@
     </row>
     <row r="201" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>1068</v>
@@ -68827,7 +68839,7 @@
         <v>2161</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>988</v>
+        <v>1127</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>333</v>
@@ -68854,7 +68866,7 @@
     </row>
     <row r="202" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
-        <v>1110</v>
+        <v>1128</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>1068</v>
@@ -68866,7 +68878,7 @@
         <v>2162</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>805</v>
+        <v>975</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>333</v>
@@ -68893,7 +68905,7 @@
     </row>
     <row r="203" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>1068</v>
@@ -68905,7 +68917,7 @@
         <v>2163</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>333</v>
@@ -68932,7 +68944,7 @@
     </row>
     <row r="204" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>1068</v>
@@ -68944,7 +68956,7 @@
         <v>2164</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>815</v>
+        <v>805</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>333</v>
@@ -68971,7 +68983,7 @@
     </row>
     <row r="205" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A205" s="3" t="s">
-        <v>1113</v>
+        <v>1132</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>1068</v>
@@ -68983,7 +68995,7 @@
         <v>2165</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>1087</v>
+        <v>990</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>333</v>
@@ -69010,7 +69022,7 @@
     </row>
     <row r="206" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>1068</v>
@@ -69022,7 +69034,7 @@
         <v>2166</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>333</v>
@@ -69049,7 +69061,7 @@
     </row>
     <row r="207" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>1068</v>
@@ -69061,7 +69073,7 @@
         <v>2167</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>333</v>
@@ -69088,7 +69100,7 @@
     </row>
     <row r="208" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>1068</v>
@@ -69100,7 +69112,7 @@
         <v>2168</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>1075</v>
+        <v>810</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>333</v>
@@ -69127,7 +69139,7 @@
     </row>
     <row r="209" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>1068</v>
@@ -69139,7 +69151,7 @@
         <v>2169</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>333</v>
@@ -69166,7 +69178,7 @@
     </row>
     <row r="210" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>1068</v>
@@ -69178,7 +69190,7 @@
         <v>2170</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>837</v>
+        <v>1075</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>333</v>
@@ -69205,7 +69217,7 @@
     </row>
     <row r="211" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>1068</v>
@@ -69217,7 +69229,7 @@
         <v>2171</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>966</v>
+        <v>1093</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>333</v>
@@ -69244,7 +69256,7 @@
     </row>
     <row r="212" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="B212" s="3" t="s">
         <v>1068</v>
@@ -69256,7 +69268,7 @@
         <v>2172</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>1097</v>
+        <v>837</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>333</v>
@@ -69283,7 +69295,7 @@
     </row>
     <row r="213" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="B213" s="3" t="s">
         <v>1068</v>
@@ -69295,7 +69307,7 @@
         <v>2173</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>1122</v>
+        <v>966</v>
       </c>
       <c r="F213" s="3" t="s">
         <v>333</v>
@@ -69322,7 +69334,7 @@
     </row>
     <row r="214" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="B214" s="3" t="s">
         <v>1068</v>
@@ -69334,7 +69346,7 @@
         <v>2174</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>1124</v>
+        <v>1097</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>333</v>
@@ -69361,7 +69373,7 @@
     </row>
     <row r="215" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="B215" s="3" t="s">
         <v>1068</v>
@@ -69373,7 +69385,7 @@
         <v>2175</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>968</v>
+        <v>1122</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>333</v>
@@ -69400,7 +69412,7 @@
     </row>
     <row r="216" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
-        <v>1128</v>
+        <v>1123</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>1068</v>
@@ -69412,7 +69424,7 @@
         <v>2176</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>975</v>
+        <v>1124</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>333</v>
@@ -69439,7 +69451,7 @@
     </row>
     <row r="217" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A217" s="3" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="B217" s="3" t="s">
         <v>1068</v>
@@ -69451,7 +69463,7 @@
         <v>2177</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>988</v>
+        <v>968</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>333</v>
@@ -69478,7 +69490,7 @@
     </row>
     <row r="218" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A218" s="3" t="s">
-        <v>1110</v>
+        <v>1128</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>1068</v>
@@ -69490,7 +69502,7 @@
         <v>2178</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>805</v>
+        <v>975</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>333</v>
@@ -69517,7 +69529,7 @@
     </row>
     <row r="219" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A219" s="3" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="B219" s="3" t="s">
         <v>1068</v>
@@ -69529,7 +69541,7 @@
         <v>2179</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>333</v>
@@ -69556,7 +69568,7 @@
     </row>
     <row r="220" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="B220" s="3" t="s">
         <v>1068</v>
@@ -69568,7 +69580,7 @@
         <v>2180</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>815</v>
+        <v>805</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>333</v>
@@ -69595,7 +69607,7 @@
     </row>
     <row r="221" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
-        <v>1114</v>
+        <v>1132</v>
       </c>
       <c r="B221" s="3" t="s">
         <v>1068</v>
@@ -69607,7 +69619,7 @@
         <v>2181</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>810</v>
+        <v>990</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>333</v>
@@ -69634,7 +69646,7 @@
     </row>
     <row r="222" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A222" s="3" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="B222" s="3" t="s">
         <v>1068</v>
@@ -69646,7 +69658,7 @@
         <v>2182</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>1075</v>
+        <v>815</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>333</v>
@@ -69673,7 +69685,7 @@
     </row>
     <row r="223" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A223" s="3" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
       <c r="B223" s="3" t="s">
         <v>1068</v>
@@ -69685,7 +69697,7 @@
         <v>2183</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>837</v>
+        <v>810</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>333</v>
@@ -69712,7 +69724,7 @@
     </row>
     <row r="224" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="B224" s="3" t="s">
         <v>1068</v>
@@ -69724,7 +69736,7 @@
         <v>2184</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>966</v>
+        <v>1075</v>
       </c>
       <c r="F224" s="3" t="s">
         <v>333</v>
@@ -69751,7 +69763,7 @@
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A225" s="3" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="B225" s="3" t="s">
         <v>1068</v>
@@ -69763,7 +69775,7 @@
         <v>2185</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>1097</v>
+        <v>837</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>333</v>
@@ -69790,7 +69802,7 @@
     </row>
     <row r="226" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A226" s="3" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="B226" s="3" t="s">
         <v>1068</v>
@@ -69802,7 +69814,7 @@
         <v>2186</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>1122</v>
+        <v>966</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>333</v>
@@ -69829,7 +69841,7 @@
     </row>
     <row r="227" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A227" s="3" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="B227" s="3" t="s">
         <v>1068</v>
@@ -69841,7 +69853,7 @@
         <v>2187</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>1124</v>
+        <v>1097</v>
       </c>
       <c r="F227" s="3" t="s">
         <v>333</v>
@@ -69868,7 +69880,7 @@
     </row>
     <row r="228" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="B228" s="3" t="s">
         <v>1068</v>
@@ -69880,7 +69892,7 @@
         <v>2188</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>968</v>
+        <v>1122</v>
       </c>
       <c r="F228" s="3" t="s">
         <v>333</v>
@@ -69907,7 +69919,7 @@
     </row>
     <row r="229" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A229" s="3" t="s">
-        <v>1128</v>
+        <v>1123</v>
       </c>
       <c r="B229" s="3" t="s">
         <v>1068</v>
@@ -69919,7 +69931,7 @@
         <v>2189</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>975</v>
+        <v>1124</v>
       </c>
       <c r="F229" s="3" t="s">
         <v>333</v>
@@ -69946,7 +69958,7 @@
     </row>
     <row r="230" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="B230" s="3" t="s">
         <v>1068</v>
@@ -69958,7 +69970,7 @@
         <v>2190</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>988</v>
+        <v>968</v>
       </c>
       <c r="F230" s="3" t="s">
         <v>333</v>
@@ -69985,7 +69997,7 @@
     </row>
     <row r="231" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A231" s="3" t="s">
-        <v>1110</v>
+        <v>1126</v>
       </c>
       <c r="B231" s="3" t="s">
         <v>1068</v>
@@ -69997,7 +70009,7 @@
         <v>2191</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>805</v>
+        <v>1127</v>
       </c>
       <c r="F231" s="3" t="s">
         <v>333</v>
@@ -70024,7 +70036,7 @@
     </row>
     <row r="232" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A232" s="3" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="B232" s="3" t="s">
         <v>1068</v>
@@ -70036,7 +70048,7 @@
         <v>2192</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>990</v>
+        <v>975</v>
       </c>
       <c r="F232" s="3" t="s">
         <v>333</v>
@@ -70063,7 +70075,7 @@
     </row>
     <row r="233" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A233" s="3" t="s">
-        <v>1112</v>
+        <v>1129</v>
       </c>
       <c r="B233" s="3" t="s">
         <v>1068</v>
@@ -70075,7 +70087,7 @@
         <v>2193</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>815</v>
+        <v>988</v>
       </c>
       <c r="F233" s="3" t="s">
         <v>333</v>
@@ -70102,7 +70114,7 @@
     </row>
     <row r="234" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="B234" s="3" t="s">
         <v>1068</v>
@@ -70114,7 +70126,7 @@
         <v>2194</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>1087</v>
+        <v>805</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>333</v>
@@ -70141,7 +70153,7 @@
     </row>
     <row r="235" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A235" s="3" t="s">
-        <v>1114</v>
+        <v>1132</v>
       </c>
       <c r="B235" s="3" t="s">
         <v>1068</v>
@@ -70153,7 +70165,7 @@
         <v>2195</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>810</v>
+        <v>990</v>
       </c>
       <c r="F235" s="3" t="s">
         <v>333</v>
@@ -70180,7 +70192,7 @@
     </row>
     <row r="236" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="B236" s="3" t="s">
         <v>1068</v>
@@ -70192,7 +70204,7 @@
         <v>2196</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>1090</v>
+        <v>815</v>
       </c>
       <c r="F236" s="3" t="s">
         <v>333</v>
@@ -70219,7 +70231,7 @@
     </row>
     <row r="237" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="B237" s="3" t="s">
         <v>1068</v>
@@ -70231,7 +70243,7 @@
         <v>2197</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>1075</v>
+        <v>1087</v>
       </c>
       <c r="F237" s="3" t="s">
         <v>333</v>
@@ -70258,7 +70270,7 @@
     </row>
     <row r="238" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A238" s="3" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="B238" s="3" t="s">
         <v>1068</v>
@@ -70270,7 +70282,7 @@
         <v>2198</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>1093</v>
+        <v>810</v>
       </c>
       <c r="F238" s="3" t="s">
         <v>333</v>
@@ -70297,7 +70309,7 @@
     </row>
     <row r="239" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A239" s="3" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="B239" s="3" t="s">
         <v>1068</v>
@@ -70309,7 +70321,7 @@
         <v>2199</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>837</v>
+        <v>1090</v>
       </c>
       <c r="F239" s="3" t="s">
         <v>333</v>
@@ -70336,7 +70348,7 @@
     </row>
     <row r="240" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="B240" s="3" t="s">
         <v>1068</v>
@@ -70348,7 +70360,7 @@
         <v>2200</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>966</v>
+        <v>1075</v>
       </c>
       <c r="F240" s="3" t="s">
         <v>333</v>
@@ -70375,7 +70387,7 @@
     </row>
     <row r="241" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A241" s="3" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="B241" s="3" t="s">
         <v>1068</v>
@@ -70387,7 +70399,7 @@
         <v>2201</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="F241" s="3" t="s">
         <v>333</v>
@@ -70414,7 +70426,7 @@
     </row>
     <row r="242" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A242" s="3" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="B242" s="3" t="s">
         <v>1068</v>
@@ -70426,7 +70438,7 @@
         <v>2202</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>1122</v>
+        <v>837</v>
       </c>
       <c r="F242" s="3" t="s">
         <v>333</v>
@@ -70453,7 +70465,7 @@
     </row>
     <row r="243" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A243" s="3" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
       <c r="B243" s="3" t="s">
         <v>1068</v>
@@ -70465,7 +70477,7 @@
         <v>2203</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>1124</v>
+        <v>966</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>333</v>
@@ -70492,7 +70504,7 @@
     </row>
     <row r="244" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A244" s="3" t="s">
-        <v>1125</v>
+        <v>1120</v>
       </c>
       <c r="B244" s="3" t="s">
         <v>1068</v>
@@ -70504,7 +70516,7 @@
         <v>2204</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>968</v>
+        <v>1097</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>333</v>
@@ -70513,10 +70525,10 @@
         <v>7</v>
       </c>
       <c r="H244" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I244" s="4" t="s">
-        <v>16</v>
+        <v>2204</v>
       </c>
       <c r="J244" s="3" t="s">
         <v>333</v>
@@ -70531,7 +70543,7 @@
     </row>
     <row r="245" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A245" s="3" t="s">
-        <v>1128</v>
+        <v>1121</v>
       </c>
       <c r="B245" s="3" t="s">
         <v>1068</v>
@@ -70543,7 +70555,7 @@
         <v>2205</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>975</v>
+        <v>1122</v>
       </c>
       <c r="F245" s="3" t="s">
         <v>333</v>
@@ -70552,10 +70564,10 @@
         <v>7</v>
       </c>
       <c r="H245" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I245" s="4" t="s">
-        <v>16</v>
+        <v>2205</v>
       </c>
       <c r="J245" s="3" t="s">
         <v>333</v>
@@ -70570,7 +70582,7 @@
     </row>
     <row r="246" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A246" s="3" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
       <c r="B246" s="3" t="s">
         <v>1068</v>
@@ -70582,7 +70594,7 @@
         <v>2206</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>988</v>
+        <v>1124</v>
       </c>
       <c r="F246" s="3" t="s">
         <v>333</v>
@@ -70591,10 +70603,10 @@
         <v>7</v>
       </c>
       <c r="H246" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I246" s="4" t="s">
-        <v>16</v>
+        <v>2206</v>
       </c>
       <c r="J246" s="3" t="s">
         <v>333</v>
@@ -70609,7 +70621,7 @@
     </row>
     <row r="247" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A247" s="3" t="s">
-        <v>1110</v>
+        <v>1125</v>
       </c>
       <c r="B247" s="3" t="s">
         <v>1068</v>
@@ -70621,7 +70633,7 @@
         <v>2207</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>805</v>
+        <v>968</v>
       </c>
       <c r="F247" s="3" t="s">
         <v>333</v>
@@ -70648,7 +70660,7 @@
     </row>
     <row r="248" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A248" s="3" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="B248" s="3" t="s">
         <v>1068</v>
@@ -70660,7 +70672,7 @@
         <v>2208</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>990</v>
+        <v>975</v>
       </c>
       <c r="F248" s="3" t="s">
         <v>333</v>
@@ -70687,7 +70699,7 @@
     </row>
     <row r="249" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A249" s="3" t="s">
-        <v>1112</v>
+        <v>1129</v>
       </c>
       <c r="B249" s="3" t="s">
         <v>1068</v>
@@ -70699,7 +70711,7 @@
         <v>2209</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>815</v>
+        <v>988</v>
       </c>
       <c r="F249" s="3" t="s">
         <v>333</v>
@@ -70726,7 +70738,7 @@
     </row>
     <row r="250" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A250" s="3" t="s">
-        <v>1114</v>
+        <v>1110</v>
       </c>
       <c r="B250" s="3" t="s">
         <v>1068</v>
@@ -70738,7 +70750,7 @@
         <v>2210</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="F250" s="3" t="s">
         <v>333</v>
@@ -70765,7 +70777,7 @@
     </row>
     <row r="251" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A251" s="3" t="s">
-        <v>1116</v>
+        <v>1132</v>
       </c>
       <c r="B251" s="3" t="s">
         <v>1068</v>
@@ -70777,7 +70789,7 @@
         <v>2211</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>1075</v>
+        <v>990</v>
       </c>
       <c r="F251" s="3" t="s">
         <v>333</v>
@@ -70804,7 +70816,7 @@
     </row>
     <row r="252" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A252" s="3" t="s">
-        <v>1118</v>
+        <v>1112</v>
       </c>
       <c r="B252" s="3" t="s">
         <v>1068</v>
@@ -70816,7 +70828,7 @@
         <v>2212</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>837</v>
+        <v>815</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>333</v>
@@ -70843,7 +70855,7 @@
     </row>
     <row r="253" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A253" s="3" t="s">
-        <v>1119</v>
+        <v>1114</v>
       </c>
       <c r="B253" s="3" t="s">
         <v>1068</v>
@@ -70855,7 +70867,7 @@
         <v>2213</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>966</v>
+        <v>810</v>
       </c>
       <c r="F253" s="3" t="s">
         <v>333</v>
@@ -70882,7 +70894,7 @@
     </row>
     <row r="254" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A254" s="3" t="s">
-        <v>1120</v>
+        <v>1116</v>
       </c>
       <c r="B254" s="3" t="s">
         <v>1068</v>
@@ -70894,7 +70906,7 @@
         <v>2214</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>1097</v>
+        <v>1075</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>333</v>
@@ -70921,7 +70933,7 @@
     </row>
     <row r="255" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A255" s="3" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="B255" s="3" t="s">
         <v>1068</v>
@@ -70933,7 +70945,7 @@
         <v>2215</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>1122</v>
+        <v>837</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>333</v>
@@ -70960,7 +70972,7 @@
     </row>
     <row r="256" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A256" s="3" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
       <c r="B256" s="3" t="s">
         <v>1068</v>
@@ -70972,7 +70984,7 @@
         <v>2216</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>1124</v>
+        <v>966</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>333</v>
@@ -70999,7 +71011,7 @@
     </row>
     <row r="257" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
-        <v>1125</v>
+        <v>1120</v>
       </c>
       <c r="B257" s="3" t="s">
         <v>1068</v>
@@ -71011,7 +71023,7 @@
         <v>2217</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>968</v>
+        <v>1097</v>
       </c>
       <c r="F257" s="3" t="s">
         <v>333</v>
@@ -71020,10 +71032,10 @@
         <v>7</v>
       </c>
       <c r="H257" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I257" s="4" t="s">
-        <v>2217</v>
+        <v>16</v>
       </c>
       <c r="J257" s="3" t="s">
         <v>333</v>
@@ -71038,7 +71050,7 @@
     </row>
     <row r="258" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A258" s="3" t="s">
-        <v>1128</v>
+        <v>1121</v>
       </c>
       <c r="B258" s="3" t="s">
         <v>1068</v>
@@ -71050,7 +71062,7 @@
         <v>2218</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>975</v>
+        <v>1122</v>
       </c>
       <c r="F258" s="3" t="s">
         <v>333</v>
@@ -71059,10 +71071,10 @@
         <v>7</v>
       </c>
       <c r="H258" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I258" s="4" t="s">
-        <v>2218</v>
+        <v>16</v>
       </c>
       <c r="J258" s="3" t="s">
         <v>333</v>
@@ -71077,7 +71089,7 @@
     </row>
     <row r="259" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A259" s="3" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
       <c r="B259" s="3" t="s">
         <v>1068</v>
@@ -71089,7 +71101,7 @@
         <v>2219</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>988</v>
+        <v>1124</v>
       </c>
       <c r="F259" s="3" t="s">
         <v>333</v>
@@ -71098,10 +71110,10 @@
         <v>7</v>
       </c>
       <c r="H259" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I259" s="4" t="s">
-        <v>2219</v>
+        <v>16</v>
       </c>
       <c r="J259" s="3" t="s">
         <v>333</v>
@@ -71116,7 +71128,7 @@
     </row>
     <row r="260" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A260" s="3" t="s">
-        <v>1110</v>
+        <v>1125</v>
       </c>
       <c r="B260" s="3" t="s">
         <v>1068</v>
@@ -71128,7 +71140,7 @@
         <v>2220</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>805</v>
+        <v>968</v>
       </c>
       <c r="F260" s="3" t="s">
         <v>333</v>
@@ -71155,7 +71167,7 @@
     </row>
     <row r="261" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A261" s="3" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="B261" s="3" t="s">
         <v>1068</v>
@@ -71167,7 +71179,7 @@
         <v>2221</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>990</v>
+        <v>975</v>
       </c>
       <c r="F261" s="3" t="s">
         <v>333</v>
@@ -71194,7 +71206,7 @@
     </row>
     <row r="262" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A262" s="3" t="s">
-        <v>1112</v>
+        <v>1129</v>
       </c>
       <c r="B262" s="3" t="s">
         <v>1068</v>
@@ -71206,7 +71218,7 @@
         <v>2222</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>815</v>
+        <v>988</v>
       </c>
       <c r="F262" s="3" t="s">
         <v>333</v>
@@ -71233,7 +71245,7 @@
     </row>
     <row r="263" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A263" s="3" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="B263" s="3" t="s">
         <v>1068</v>
@@ -71245,7 +71257,7 @@
         <v>2223</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>1087</v>
+        <v>805</v>
       </c>
       <c r="F263" s="3" t="s">
         <v>333</v>
@@ -71272,7 +71284,7 @@
     </row>
     <row r="264" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A264" s="3" t="s">
-        <v>1114</v>
+        <v>1132</v>
       </c>
       <c r="B264" s="3" t="s">
         <v>1068</v>
@@ -71284,7 +71296,7 @@
         <v>2224</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>810</v>
+        <v>990</v>
       </c>
       <c r="F264" s="3" t="s">
         <v>333</v>
@@ -71311,7 +71323,7 @@
     </row>
     <row r="265" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A265" s="3" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="B265" s="3" t="s">
         <v>1068</v>
@@ -71323,7 +71335,7 @@
         <v>2225</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>1090</v>
+        <v>815</v>
       </c>
       <c r="F265" s="3" t="s">
         <v>333</v>
@@ -71350,7 +71362,7 @@
     </row>
     <row r="266" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A266" s="3" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="B266" s="3" t="s">
         <v>1068</v>
@@ -71362,7 +71374,7 @@
         <v>2226</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>1075</v>
+        <v>1087</v>
       </c>
       <c r="F266" s="3" t="s">
         <v>333</v>
@@ -71389,7 +71401,7 @@
     </row>
     <row r="267" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A267" s="3" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="B267" s="3" t="s">
         <v>1068</v>
@@ -71401,7 +71413,7 @@
         <v>2227</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>1093</v>
+        <v>810</v>
       </c>
       <c r="F267" s="3" t="s">
         <v>333</v>
@@ -71428,7 +71440,7 @@
     </row>
     <row r="268" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A268" s="3" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="B268" s="3" t="s">
         <v>1068</v>
@@ -71440,7 +71452,7 @@
         <v>2228</v>
       </c>
       <c r="E268" s="3" t="s">
-        <v>837</v>
+        <v>1090</v>
       </c>
       <c r="F268" s="3" t="s">
         <v>333</v>
@@ -71467,7 +71479,7 @@
     </row>
     <row r="269" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A269" s="3" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="B269" s="3" t="s">
         <v>1068</v>
@@ -71479,7 +71491,7 @@
         <v>2229</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>966</v>
+        <v>1075</v>
       </c>
       <c r="F269" s="3" t="s">
         <v>333</v>
@@ -71506,7 +71518,7 @@
     </row>
     <row r="270" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A270" s="3" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="B270" s="3" t="s">
         <v>1068</v>
@@ -71518,7 +71530,7 @@
         <v>2230</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>333</v>
@@ -71545,7 +71557,7 @@
     </row>
     <row r="271" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A271" s="3" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="B271" s="3" t="s">
         <v>1068</v>
@@ -71557,7 +71569,7 @@
         <v>2231</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>1122</v>
+        <v>837</v>
       </c>
       <c r="F271" s="3" t="s">
         <v>333</v>
@@ -71584,7 +71596,7 @@
     </row>
     <row r="272" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A272" s="3" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
       <c r="B272" s="3" t="s">
         <v>1068</v>
@@ -71596,7 +71608,7 @@
         <v>2232</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>1124</v>
+        <v>966</v>
       </c>
       <c r="F272" s="3" t="s">
         <v>333</v>
@@ -71623,7 +71635,7 @@
     </row>
     <row r="273" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A273" s="3" t="s">
-        <v>1125</v>
+        <v>1120</v>
       </c>
       <c r="B273" s="3" t="s">
         <v>1068</v>
@@ -71635,7 +71647,7 @@
         <v>2233</v>
       </c>
       <c r="E273" s="3" t="s">
-        <v>968</v>
+        <v>1097</v>
       </c>
       <c r="F273" s="3" t="s">
         <v>333</v>
@@ -71662,7 +71674,7 @@
     </row>
     <row r="274" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A274" s="3" t="s">
-        <v>1128</v>
+        <v>1121</v>
       </c>
       <c r="B274" s="3" t="s">
         <v>1068</v>
@@ -71674,7 +71686,7 @@
         <v>2234</v>
       </c>
       <c r="E274" s="3" t="s">
-        <v>975</v>
+        <v>1122</v>
       </c>
       <c r="F274" s="3" t="s">
         <v>333</v>
@@ -71701,7 +71713,7 @@
     </row>
     <row r="275" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A275" s="3" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
       <c r="B275" s="3" t="s">
         <v>1068</v>
@@ -71713,7 +71725,7 @@
         <v>2235</v>
       </c>
       <c r="E275" s="3" t="s">
-        <v>988</v>
+        <v>1124</v>
       </c>
       <c r="F275" s="3" t="s">
         <v>333</v>
@@ -71740,7 +71752,7 @@
     </row>
     <row r="276" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A276" s="3" t="s">
-        <v>1110</v>
+        <v>1125</v>
       </c>
       <c r="B276" s="3" t="s">
         <v>1068</v>
@@ -71752,7 +71764,7 @@
         <v>2236</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>805</v>
+        <v>968</v>
       </c>
       <c r="F276" s="3" t="s">
         <v>333</v>
@@ -71779,7 +71791,7 @@
     </row>
     <row r="277" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A277" s="3" t="s">
-        <v>1132</v>
+        <v>1126</v>
       </c>
       <c r="B277" s="3" t="s">
         <v>1068</v>
@@ -71791,7 +71803,7 @@
         <v>2237</v>
       </c>
       <c r="E277" s="3" t="s">
-        <v>990</v>
+        <v>1127</v>
       </c>
       <c r="F277" s="3" t="s">
         <v>333</v>
@@ -71818,7 +71830,7 @@
     </row>
     <row r="278" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A278" s="3" t="s">
-        <v>1112</v>
+        <v>1128</v>
       </c>
       <c r="B278" s="3" t="s">
         <v>1068</v>
@@ -71830,7 +71842,7 @@
         <v>2238</v>
       </c>
       <c r="E278" s="3" t="s">
-        <v>815</v>
+        <v>975</v>
       </c>
       <c r="F278" s="3" t="s">
         <v>333</v>
@@ -71857,7 +71869,7 @@
     </row>
     <row r="279" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A279" s="3" t="s">
-        <v>1113</v>
+        <v>1129</v>
       </c>
       <c r="B279" s="3" t="s">
         <v>1068</v>
@@ -71869,7 +71881,7 @@
         <v>2239</v>
       </c>
       <c r="E279" s="3" t="s">
-        <v>1087</v>
+        <v>988</v>
       </c>
       <c r="F279" s="3" t="s">
         <v>333</v>
@@ -71896,7 +71908,7 @@
     </row>
     <row r="280" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A280" s="3" t="s">
-        <v>1114</v>
+        <v>1110</v>
       </c>
       <c r="B280" s="3" t="s">
         <v>1068</v>
@@ -71908,7 +71920,7 @@
         <v>2240</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="F280" s="3" t="s">
         <v>333</v>
@@ -71935,7 +71947,7 @@
     </row>
     <row r="281" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A281" s="3" t="s">
-        <v>1115</v>
+        <v>1132</v>
       </c>
       <c r="B281" s="3" t="s">
         <v>1068</v>
@@ -71947,7 +71959,7 @@
         <v>2241</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>1090</v>
+        <v>990</v>
       </c>
       <c r="F281" s="3" t="s">
         <v>333</v>
@@ -71974,7 +71986,7 @@
     </row>
     <row r="282" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A282" s="3" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="B282" s="3" t="s">
         <v>1068</v>
@@ -71986,7 +71998,7 @@
         <v>2242</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>1075</v>
+        <v>815</v>
       </c>
       <c r="F282" s="3" t="s">
         <v>333</v>
@@ -72013,7 +72025,7 @@
     </row>
     <row r="283" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A283" s="3" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="B283" s="3" t="s">
         <v>1068</v>
@@ -72025,7 +72037,7 @@
         <v>2243</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F283" s="3" t="s">
         <v>333</v>
@@ -72052,7 +72064,7 @@
     </row>
     <row r="284" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A284" s="3" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
       <c r="B284" s="3" t="s">
         <v>1068</v>
@@ -72064,7 +72076,7 @@
         <v>2244</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>837</v>
+        <v>810</v>
       </c>
       <c r="F284" s="3" t="s">
         <v>333</v>
@@ -72091,7 +72103,7 @@
     </row>
     <row r="285" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A285" s="3" t="s">
-        <v>1119</v>
+        <v>1115</v>
       </c>
       <c r="B285" s="3" t="s">
         <v>1068</v>
@@ -72103,7 +72115,7 @@
         <v>2245</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>966</v>
+        <v>1090</v>
       </c>
       <c r="F285" s="3" t="s">
         <v>333</v>
@@ -72130,7 +72142,7 @@
     </row>
     <row r="286" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A286" s="3" t="s">
-        <v>1120</v>
+        <v>1116</v>
       </c>
       <c r="B286" s="3" t="s">
         <v>1068</v>
@@ -72142,7 +72154,7 @@
         <v>2246</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>1097</v>
+        <v>1075</v>
       </c>
       <c r="F286" s="3" t="s">
         <v>333</v>
@@ -72169,7 +72181,7 @@
     </row>
     <row r="287" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A287" s="3" t="s">
-        <v>1121</v>
+        <v>1117</v>
       </c>
       <c r="B287" s="3" t="s">
         <v>1068</v>
@@ -72181,7 +72193,7 @@
         <v>2247</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>1122</v>
+        <v>1093</v>
       </c>
       <c r="F287" s="3" t="s">
         <v>333</v>
@@ -72208,7 +72220,7 @@
     </row>
     <row r="288" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A288" s="3" t="s">
-        <v>1123</v>
+        <v>1118</v>
       </c>
       <c r="B288" s="3" t="s">
         <v>1068</v>
@@ -72220,7 +72232,7 @@
         <v>2248</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>1124</v>
+        <v>837</v>
       </c>
       <c r="F288" s="3" t="s">
         <v>333</v>
@@ -72247,7 +72259,7 @@
     </row>
     <row r="289" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A289" s="3" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="B289" s="3" t="s">
         <v>1068</v>
@@ -72259,7 +72271,7 @@
         <v>2249</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="F289" s="3" t="s">
         <v>333</v>
@@ -72268,10 +72280,10 @@
         <v>7</v>
       </c>
       <c r="H289" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I289" s="4" t="s">
-        <v>16</v>
+        <v>2249</v>
       </c>
       <c r="J289" s="3" t="s">
         <v>333</v>
@@ -72286,7 +72298,7 @@
     </row>
     <row r="290" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A290" s="3" t="s">
-        <v>1128</v>
+        <v>1120</v>
       </c>
       <c r="B290" s="3" t="s">
         <v>1068</v>
@@ -72298,7 +72310,7 @@
         <v>2250</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>975</v>
+        <v>1097</v>
       </c>
       <c r="F290" s="3" t="s">
         <v>333</v>
@@ -72307,10 +72319,10 @@
         <v>7</v>
       </c>
       <c r="H290" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I290" s="4" t="s">
-        <v>16</v>
+        <v>2250</v>
       </c>
       <c r="J290" s="3" t="s">
         <v>333</v>
@@ -72325,7 +72337,7 @@
     </row>
     <row r="291" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A291" s="3" t="s">
-        <v>1129</v>
+        <v>1121</v>
       </c>
       <c r="B291" s="3" t="s">
         <v>1068</v>
@@ -72337,7 +72349,7 @@
         <v>2251</v>
       </c>
       <c r="E291" s="3" t="s">
-        <v>988</v>
+        <v>1122</v>
       </c>
       <c r="F291" s="3" t="s">
         <v>333</v>
@@ -72346,10 +72358,10 @@
         <v>7</v>
       </c>
       <c r="H291" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I291" s="4" t="s">
-        <v>16</v>
+        <v>2251</v>
       </c>
       <c r="J291" s="3" t="s">
         <v>333</v>
@@ -72364,7 +72376,7 @@
     </row>
     <row r="292" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A292" s="3" t="s">
-        <v>1110</v>
+        <v>1123</v>
       </c>
       <c r="B292" s="3" t="s">
         <v>1068</v>
@@ -72376,7 +72388,7 @@
         <v>2252</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>805</v>
+        <v>1124</v>
       </c>
       <c r="F292" s="3" t="s">
         <v>333</v>
@@ -72385,10 +72397,10 @@
         <v>7</v>
       </c>
       <c r="H292" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I292" s="4" t="s">
-        <v>16</v>
+        <v>2252</v>
       </c>
       <c r="J292" s="3" t="s">
         <v>333</v>
@@ -72403,7 +72415,7 @@
     </row>
     <row r="293" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A293" s="3" t="s">
-        <v>1132</v>
+        <v>1125</v>
       </c>
       <c r="B293" s="3" t="s">
         <v>1068</v>
@@ -72415,7 +72427,7 @@
         <v>2253</v>
       </c>
       <c r="E293" s="3" t="s">
-        <v>990</v>
+        <v>968</v>
       </c>
       <c r="F293" s="3" t="s">
         <v>333</v>
@@ -72442,7 +72454,7 @@
     </row>
     <row r="294" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A294" s="3" t="s">
-        <v>1112</v>
+        <v>1128</v>
       </c>
       <c r="B294" s="3" t="s">
         <v>1068</v>
@@ -72454,7 +72466,7 @@
         <v>2254</v>
       </c>
       <c r="E294" s="3" t="s">
-        <v>815</v>
+        <v>975</v>
       </c>
       <c r="F294" s="3" t="s">
         <v>333</v>
@@ -72481,7 +72493,7 @@
     </row>
     <row r="295" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A295" s="3" t="s">
-        <v>1114</v>
+        <v>1129</v>
       </c>
       <c r="B295" s="3" t="s">
         <v>1068</v>
@@ -72493,7 +72505,7 @@
         <v>2255</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>810</v>
+        <v>988</v>
       </c>
       <c r="F295" s="3" t="s">
         <v>333</v>
@@ -72520,7 +72532,7 @@
     </row>
     <row r="296" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A296" s="3" t="s">
-        <v>1116</v>
+        <v>1110</v>
       </c>
       <c r="B296" s="3" t="s">
         <v>1068</v>
@@ -72532,7 +72544,7 @@
         <v>2256</v>
       </c>
       <c r="E296" s="3" t="s">
-        <v>1075</v>
+        <v>805</v>
       </c>
       <c r="F296" s="3" t="s">
         <v>333</v>
@@ -72559,7 +72571,7 @@
     </row>
     <row r="297" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A297" s="3" t="s">
-        <v>1118</v>
+        <v>1132</v>
       </c>
       <c r="B297" s="3" t="s">
         <v>1068</v>
@@ -72571,7 +72583,7 @@
         <v>2257</v>
       </c>
       <c r="E297" s="3" t="s">
-        <v>837</v>
+        <v>990</v>
       </c>
       <c r="F297" s="3" t="s">
         <v>333</v>
@@ -72598,7 +72610,7 @@
     </row>
     <row r="298" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A298" s="3" t="s">
-        <v>1119</v>
+        <v>1112</v>
       </c>
       <c r="B298" s="3" t="s">
         <v>1068</v>
@@ -72610,7 +72622,7 @@
         <v>2258</v>
       </c>
       <c r="E298" s="3" t="s">
-        <v>966</v>
+        <v>815</v>
       </c>
       <c r="F298" s="3" t="s">
         <v>333</v>
@@ -72637,7 +72649,7 @@
     </row>
     <row r="299" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A299" s="3" t="s">
-        <v>1120</v>
+        <v>1114</v>
       </c>
       <c r="B299" s="3" t="s">
         <v>1068</v>
@@ -72649,7 +72661,7 @@
         <v>2259</v>
       </c>
       <c r="E299" s="3" t="s">
-        <v>1097</v>
+        <v>810</v>
       </c>
       <c r="F299" s="3" t="s">
         <v>333</v>
@@ -72676,7 +72688,7 @@
     </row>
     <row r="300" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A300" s="3" t="s">
-        <v>1121</v>
+        <v>1116</v>
       </c>
       <c r="B300" s="3" t="s">
         <v>1068</v>
@@ -72688,7 +72700,7 @@
         <v>2260</v>
       </c>
       <c r="E300" s="3" t="s">
-        <v>1122</v>
+        <v>1075</v>
       </c>
       <c r="F300" s="3" t="s">
         <v>333</v>
@@ -72715,7 +72727,7 @@
     </row>
     <row r="301" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A301" s="3" t="s">
-        <v>1123</v>
+        <v>1118</v>
       </c>
       <c r="B301" s="3" t="s">
         <v>1068</v>
@@ -72727,7 +72739,7 @@
         <v>2261</v>
       </c>
       <c r="E301" s="3" t="s">
-        <v>1124</v>
+        <v>837</v>
       </c>
       <c r="F301" s="3" t="s">
         <v>333</v>
@@ -72754,7 +72766,7 @@
     </row>
     <row r="302" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A302" s="3" t="s">
-        <v>1143</v>
+        <v>1119</v>
       </c>
       <c r="B302" s="3" t="s">
         <v>1068</v>
@@ -72766,7 +72778,7 @@
         <v>2262</v>
       </c>
       <c r="E302" s="3" t="s">
-        <v>815</v>
+        <v>966</v>
       </c>
       <c r="F302" s="3" t="s">
         <v>333</v>
@@ -72793,7 +72805,7 @@
     </row>
     <row r="303" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A303" s="3" t="s">
-        <v>1145</v>
+        <v>1120</v>
       </c>
       <c r="B303" s="3" t="s">
         <v>1068</v>
@@ -72805,7 +72817,7 @@
         <v>2263</v>
       </c>
       <c r="E303" s="3" t="s">
-        <v>810</v>
+        <v>1097</v>
       </c>
       <c r="F303" s="3" t="s">
         <v>333</v>
@@ -72832,7 +72844,7 @@
     </row>
     <row r="304" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A304" s="3" t="s">
-        <v>1143</v>
+        <v>1121</v>
       </c>
       <c r="B304" s="3" t="s">
         <v>1068</v>
@@ -72844,7 +72856,7 @@
         <v>2264</v>
       </c>
       <c r="E304" s="3" t="s">
-        <v>815</v>
+        <v>1122</v>
       </c>
       <c r="F304" s="3" t="s">
         <v>333</v>
@@ -72853,10 +72865,10 @@
         <v>7</v>
       </c>
       <c r="H304" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I304" s="4" t="s">
-        <v>2264</v>
+        <v>16</v>
       </c>
       <c r="J304" s="3" t="s">
         <v>333</v>
@@ -72871,7 +72883,7 @@
     </row>
     <row r="305" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A305" s="3" t="s">
-        <v>1145</v>
+        <v>1123</v>
       </c>
       <c r="B305" s="3" t="s">
         <v>1068</v>
@@ -72883,7 +72895,7 @@
         <v>2265</v>
       </c>
       <c r="E305" s="3" t="s">
-        <v>810</v>
+        <v>1124</v>
       </c>
       <c r="F305" s="3" t="s">
         <v>333</v>
@@ -72892,10 +72904,10 @@
         <v>7</v>
       </c>
       <c r="H305" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I305" s="4" t="s">
-        <v>2265</v>
+        <v>16</v>
       </c>
       <c r="J305" s="3" t="s">
         <v>333</v>
@@ -72931,10 +72943,10 @@
         <v>7</v>
       </c>
       <c r="H306" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I306" s="4" t="s">
-        <v>2266</v>
+        <v>16</v>
       </c>
       <c r="J306" s="3" t="s">
         <v>333</v>
@@ -72970,10 +72982,10 @@
         <v>7</v>
       </c>
       <c r="H307" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I307" s="4" t="s">
-        <v>2267</v>
+        <v>16</v>
       </c>
       <c r="J307" s="3" t="s">
         <v>333</v>
@@ -73300,7 +73312,7 @@
     </row>
     <row r="316" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A316" s="3" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="B316" s="3" t="s">
         <v>1068</v>
@@ -73321,10 +73333,10 @@
         <v>7</v>
       </c>
       <c r="H316" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I316" s="4" t="s">
-        <v>16</v>
+        <v>2276</v>
       </c>
       <c r="J316" s="3" t="s">
         <v>333</v>
@@ -73339,7 +73351,7 @@
     </row>
     <row r="317" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A317" s="3" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="B317" s="3" t="s">
         <v>1068</v>
@@ -73360,10 +73372,10 @@
         <v>7</v>
       </c>
       <c r="H317" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I317" s="4" t="s">
-        <v>16</v>
+        <v>2277</v>
       </c>
       <c r="J317" s="3" t="s">
         <v>333</v>
@@ -73378,7 +73390,7 @@
     </row>
     <row r="318" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A318" s="3" t="s">
-        <v>1150</v>
+        <v>1143</v>
       </c>
       <c r="B318" s="3" t="s">
         <v>1068</v>
@@ -73390,7 +73402,7 @@
         <v>2278</v>
       </c>
       <c r="E318" s="3" t="s">
-        <v>837</v>
+        <v>815</v>
       </c>
       <c r="F318" s="3" t="s">
         <v>333</v>
@@ -73399,10 +73411,10 @@
         <v>7</v>
       </c>
       <c r="H318" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I318" s="4" t="s">
-        <v>16</v>
+        <v>2278</v>
       </c>
       <c r="J318" s="3" t="s">
         <v>333</v>
@@ -73417,7 +73429,7 @@
     </row>
     <row r="319" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A319" s="3" t="s">
-        <v>1151</v>
+        <v>1145</v>
       </c>
       <c r="B319" s="3" t="s">
         <v>1068</v>
@@ -73429,7 +73441,7 @@
         <v>2279</v>
       </c>
       <c r="E319" s="3" t="s">
-        <v>966</v>
+        <v>810</v>
       </c>
       <c r="F319" s="3" t="s">
         <v>333</v>
@@ -73438,10 +73450,10 @@
         <v>7</v>
       </c>
       <c r="H319" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I319" s="4" t="s">
-        <v>16</v>
+        <v>2279</v>
       </c>
       <c r="J319" s="3" t="s">
         <v>333</v>
@@ -73534,7 +73546,7 @@
     </row>
     <row r="322" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A322" s="3" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
       <c r="B322" s="3" t="s">
         <v>1068</v>
@@ -73546,7 +73558,7 @@
         <v>2282</v>
       </c>
       <c r="E322" s="3" t="s">
-        <v>815</v>
+        <v>837</v>
       </c>
       <c r="F322" s="3" t="s">
         <v>333</v>
@@ -73573,7 +73585,7 @@
     </row>
     <row r="323" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A323" s="3" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="B323" s="3" t="s">
         <v>1068</v>
@@ -73585,7 +73597,7 @@
         <v>2283</v>
       </c>
       <c r="E323" s="3" t="s">
-        <v>810</v>
+        <v>966</v>
       </c>
       <c r="F323" s="3" t="s">
         <v>333</v>
@@ -73633,10 +73645,10 @@
         <v>7</v>
       </c>
       <c r="H324" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I324" s="4" t="s">
-        <v>2284</v>
+        <v>16</v>
       </c>
       <c r="J324" s="3" t="s">
         <v>333</v>
@@ -73672,10 +73684,10 @@
         <v>7</v>
       </c>
       <c r="H325" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I325" s="4" t="s">
-        <v>2285</v>
+        <v>16</v>
       </c>
       <c r="J325" s="3" t="s">
         <v>333</v>
@@ -73690,7 +73702,7 @@
     </row>
     <row r="326" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A326" s="3" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="B326" s="3" t="s">
         <v>1068</v>
@@ -73702,7 +73714,7 @@
         <v>2286</v>
       </c>
       <c r="E326" s="3" t="s">
-        <v>837</v>
+        <v>815</v>
       </c>
       <c r="F326" s="3" t="s">
         <v>333</v>
@@ -73711,10 +73723,10 @@
         <v>7</v>
       </c>
       <c r="H326" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I326" s="4" t="s">
-        <v>2286</v>
+        <v>16</v>
       </c>
       <c r="J326" s="3" t="s">
         <v>333</v>
@@ -73729,7 +73741,7 @@
     </row>
     <row r="327" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A327" s="3" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="B327" s="3" t="s">
         <v>1068</v>
@@ -73741,7 +73753,7 @@
         <v>2287</v>
       </c>
       <c r="E327" s="3" t="s">
-        <v>966</v>
+        <v>810</v>
       </c>
       <c r="F327" s="3" t="s">
         <v>333</v>
@@ -73750,10 +73762,10 @@
         <v>7</v>
       </c>
       <c r="H327" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I327" s="4" t="s">
-        <v>2287</v>
+        <v>16</v>
       </c>
       <c r="J327" s="3" t="s">
         <v>333</v>
@@ -74041,7 +74053,7 @@
     </row>
     <row r="335" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A335" s="3" t="s">
-        <v>1146</v>
+        <v>1151</v>
       </c>
       <c r="B335" s="3" t="s">
         <v>1068</v>
@@ -74053,7 +74065,7 @@
         <v>2295</v>
       </c>
       <c r="E335" s="3" t="s">
-        <v>815</v>
+        <v>966</v>
       </c>
       <c r="F335" s="3" t="s">
         <v>333</v>
@@ -74080,7 +74092,7 @@
     </row>
     <row r="336" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A336" s="3" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="B336" s="3" t="s">
         <v>1068</v>
@@ -74092,7 +74104,7 @@
         <v>2296</v>
       </c>
       <c r="E336" s="3" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="F336" s="3" t="s">
         <v>333</v>
@@ -74119,7 +74131,7 @@
     </row>
     <row r="337" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A337" s="3" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="B337" s="3" t="s">
         <v>1068</v>
@@ -74131,7 +74143,7 @@
         <v>2297</v>
       </c>
       <c r="E337" s="3" t="s">
-        <v>837</v>
+        <v>810</v>
       </c>
       <c r="F337" s="3" t="s">
         <v>333</v>
@@ -74158,7 +74170,7 @@
     </row>
     <row r="338" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A338" s="3" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="B338" s="3" t="s">
         <v>1068</v>
@@ -74170,7 +74182,7 @@
         <v>2298</v>
       </c>
       <c r="E338" s="3" t="s">
-        <v>966</v>
+        <v>837</v>
       </c>
       <c r="F338" s="3" t="s">
         <v>333</v>
@@ -74218,10 +74230,10 @@
         <v>7</v>
       </c>
       <c r="H339" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I339" s="4" t="s">
-        <v>16</v>
+        <v>2299</v>
       </c>
       <c r="J339" s="3" t="s">
         <v>333</v>
@@ -74257,10 +74269,10 @@
         <v>7</v>
       </c>
       <c r="H340" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I340" s="4" t="s">
-        <v>16</v>
+        <v>2300</v>
       </c>
       <c r="J340" s="3" t="s">
         <v>333</v>
@@ -74275,7 +74287,7 @@
     </row>
     <row r="341" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A341" s="3" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
       <c r="B341" s="3" t="s">
         <v>1068</v>
@@ -74287,7 +74299,7 @@
         <v>2301</v>
       </c>
       <c r="E341" s="3" t="s">
-        <v>815</v>
+        <v>837</v>
       </c>
       <c r="F341" s="3" t="s">
         <v>333</v>
@@ -74314,7 +74326,7 @@
     </row>
     <row r="342" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A342" s="3" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="B342" s="3" t="s">
         <v>1068</v>
@@ -74326,7 +74338,7 @@
         <v>2302</v>
       </c>
       <c r="E342" s="3" t="s">
-        <v>810</v>
+        <v>966</v>
       </c>
       <c r="F342" s="3" t="s">
         <v>333</v>
@@ -74353,7 +74365,7 @@
     </row>
     <row r="343" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A343" s="3" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="B343" s="3" t="s">
         <v>1068</v>
@@ -74365,7 +74377,7 @@
         <v>2303</v>
       </c>
       <c r="E343" s="3" t="s">
-        <v>837</v>
+        <v>815</v>
       </c>
       <c r="F343" s="3" t="s">
         <v>333</v>
@@ -74374,10 +74386,10 @@
         <v>7</v>
       </c>
       <c r="H343" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I343" s="4" t="s">
-        <v>2303</v>
+        <v>16</v>
       </c>
       <c r="J343" s="3" t="s">
         <v>333</v>
@@ -74392,7 +74404,7 @@
     </row>
     <row r="344" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A344" s="3" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="B344" s="3" t="s">
         <v>1068</v>
@@ -74404,7 +74416,7 @@
         <v>2304</v>
       </c>
       <c r="E344" s="3" t="s">
-        <v>966</v>
+        <v>810</v>
       </c>
       <c r="F344" s="3" t="s">
         <v>333</v>
@@ -74413,10 +74425,10 @@
         <v>7</v>
       </c>
       <c r="H344" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I344" s="4" t="s">
-        <v>2304</v>
+        <v>16</v>
       </c>
       <c r="J344" s="3" t="s">
         <v>333</v>
@@ -74608,10 +74620,10 @@
         <v>7</v>
       </c>
       <c r="H349" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I349" s="4" t="s">
-        <v>16</v>
+        <v>2309</v>
       </c>
       <c r="J349" s="3" t="s">
         <v>333</v>
@@ -74647,10 +74659,10 @@
         <v>7</v>
       </c>
       <c r="H350" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I350" s="4" t="s">
-        <v>16</v>
+        <v>2310</v>
       </c>
       <c r="J350" s="3" t="s">
         <v>333</v>
@@ -74665,7 +74677,7 @@
     </row>
     <row r="351" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A351" s="3" t="s">
-        <v>1168</v>
+        <v>1150</v>
       </c>
       <c r="B351" s="3" t="s">
         <v>1068</v>
@@ -74677,7 +74689,7 @@
         <v>2311</v>
       </c>
       <c r="E351" s="3" t="s">
-        <v>968</v>
+        <v>837</v>
       </c>
       <c r="F351" s="3" t="s">
         <v>333</v>
@@ -74686,10 +74698,10 @@
         <v>7</v>
       </c>
       <c r="H351" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I351" s="4" t="s">
-        <v>16</v>
+        <v>2311</v>
       </c>
       <c r="J351" s="3" t="s">
         <v>333</v>
@@ -74704,7 +74716,7 @@
     </row>
     <row r="352" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A352" s="3" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="B352" s="3" t="s">
         <v>1068</v>
@@ -74716,7 +74728,7 @@
         <v>2312</v>
       </c>
       <c r="E352" s="3" t="s">
-        <v>815</v>
+        <v>966</v>
       </c>
       <c r="F352" s="3" t="s">
         <v>333</v>
@@ -74725,10 +74737,10 @@
         <v>7</v>
       </c>
       <c r="H352" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I352" s="4" t="s">
-        <v>16</v>
+        <v>2312</v>
       </c>
       <c r="J352" s="3" t="s">
         <v>333</v>
@@ -74743,7 +74755,7 @@
     </row>
     <row r="353" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A353" s="3" t="s">
-        <v>1159</v>
+        <v>1146</v>
       </c>
       <c r="B353" s="3" t="s">
         <v>1068</v>
@@ -74755,7 +74767,7 @@
         <v>2313</v>
       </c>
       <c r="E353" s="3" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="F353" s="3" t="s">
         <v>333</v>
@@ -74782,7 +74794,7 @@
     </row>
     <row r="354" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A354" s="3" t="s">
-        <v>1161</v>
+        <v>1148</v>
       </c>
       <c r="B354" s="3" t="s">
         <v>1068</v>
@@ -74794,7 +74806,7 @@
         <v>2314</v>
       </c>
       <c r="E354" s="3" t="s">
-        <v>1075</v>
+        <v>810</v>
       </c>
       <c r="F354" s="3" t="s">
         <v>333</v>
@@ -74821,7 +74833,7 @@
     </row>
     <row r="355" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A355" s="3" t="s">
-        <v>1163</v>
+        <v>1168</v>
       </c>
       <c r="B355" s="3" t="s">
         <v>1068</v>
@@ -74833,7 +74845,7 @@
         <v>2315</v>
       </c>
       <c r="E355" s="3" t="s">
-        <v>837</v>
+        <v>968</v>
       </c>
       <c r="F355" s="3" t="s">
         <v>333</v>
@@ -74860,7 +74872,7 @@
     </row>
     <row r="356" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A356" s="3" t="s">
-        <v>1164</v>
+        <v>1157</v>
       </c>
       <c r="B356" s="3" t="s">
         <v>1068</v>
@@ -74872,7 +74884,7 @@
         <v>2316</v>
       </c>
       <c r="E356" s="3" t="s">
-        <v>966</v>
+        <v>815</v>
       </c>
       <c r="F356" s="3" t="s">
         <v>333</v>
@@ -74899,7 +74911,7 @@
     </row>
     <row r="357" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A357" s="3" t="s">
-        <v>1168</v>
+        <v>1159</v>
       </c>
       <c r="B357" s="3" t="s">
         <v>1068</v>
@@ -74911,7 +74923,7 @@
         <v>2317</v>
       </c>
       <c r="E357" s="3" t="s">
-        <v>968</v>
+        <v>810</v>
       </c>
       <c r="F357" s="3" t="s">
         <v>333</v>
@@ -74938,7 +74950,7 @@
     </row>
     <row r="358" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A358" s="3" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="B358" s="3" t="s">
         <v>1068</v>
@@ -74950,7 +74962,7 @@
         <v>2318</v>
       </c>
       <c r="E358" s="3" t="s">
-        <v>815</v>
+        <v>1075</v>
       </c>
       <c r="F358" s="3" t="s">
         <v>333</v>
@@ -74977,7 +74989,7 @@
     </row>
     <row r="359" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A359" s="3" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="B359" s="3" t="s">
         <v>1068</v>
@@ -74989,7 +75001,7 @@
         <v>2319</v>
       </c>
       <c r="E359" s="3" t="s">
-        <v>810</v>
+        <v>837</v>
       </c>
       <c r="F359" s="3" t="s">
         <v>333</v>
@@ -75016,7 +75028,7 @@
     </row>
     <row r="360" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A360" s="3" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="B360" s="3" t="s">
         <v>1068</v>
@@ -75028,7 +75040,7 @@
         <v>2320</v>
       </c>
       <c r="E360" s="3" t="s">
-        <v>1075</v>
+        <v>966</v>
       </c>
       <c r="F360" s="3" t="s">
         <v>333</v>
@@ -75055,7 +75067,7 @@
     </row>
     <row r="361" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A361" s="3" t="s">
-        <v>1163</v>
+        <v>1168</v>
       </c>
       <c r="B361" s="3" t="s">
         <v>1068</v>
@@ -75067,7 +75079,7 @@
         <v>2321</v>
       </c>
       <c r="E361" s="3" t="s">
-        <v>837</v>
+        <v>968</v>
       </c>
       <c r="F361" s="3" t="s">
         <v>333</v>
@@ -75094,7 +75106,7 @@
     </row>
     <row r="362" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A362" s="3" t="s">
-        <v>1164</v>
+        <v>1157</v>
       </c>
       <c r="B362" s="3" t="s">
         <v>1068</v>
@@ -75106,7 +75118,7 @@
         <v>2322</v>
       </c>
       <c r="E362" s="3" t="s">
-        <v>966</v>
+        <v>815</v>
       </c>
       <c r="F362" s="3" t="s">
         <v>333</v>
@@ -75133,7 +75145,7 @@
     </row>
     <row r="363" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A363" s="3" t="s">
-        <v>1168</v>
+        <v>1159</v>
       </c>
       <c r="B363" s="3" t="s">
         <v>1068</v>
@@ -75145,7 +75157,7 @@
         <v>2323</v>
       </c>
       <c r="E363" s="3" t="s">
-        <v>968</v>
+        <v>810</v>
       </c>
       <c r="F363" s="3" t="s">
         <v>333</v>
@@ -75154,10 +75166,10 @@
         <v>7</v>
       </c>
       <c r="H363" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I363" s="4" t="s">
-        <v>2323</v>
+        <v>16</v>
       </c>
       <c r="J363" s="3" t="s">
         <v>333</v>
@@ -75172,7 +75184,7 @@
     </row>
     <row r="364" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A364" s="3" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="B364" s="3" t="s">
         <v>1068</v>
@@ -75184,7 +75196,7 @@
         <v>2324</v>
       </c>
       <c r="E364" s="3" t="s">
-        <v>815</v>
+        <v>1075</v>
       </c>
       <c r="F364" s="3" t="s">
         <v>333</v>
@@ -75193,10 +75205,10 @@
         <v>7</v>
       </c>
       <c r="H364" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I364" s="4" t="s">
-        <v>2324</v>
+        <v>16</v>
       </c>
       <c r="J364" s="3" t="s">
         <v>333</v>
@@ -75211,7 +75223,7 @@
     </row>
     <row r="365" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A365" s="3" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="B365" s="3" t="s">
         <v>1068</v>
@@ -75223,7 +75235,7 @@
         <v>2325</v>
       </c>
       <c r="E365" s="3" t="s">
-        <v>810</v>
+        <v>837</v>
       </c>
       <c r="F365" s="3" t="s">
         <v>333</v>
@@ -75232,10 +75244,10 @@
         <v>7</v>
       </c>
       <c r="H365" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I365" s="4" t="s">
-        <v>2325</v>
+        <v>16</v>
       </c>
       <c r="J365" s="3" t="s">
         <v>333</v>
@@ -75250,7 +75262,7 @@
     </row>
     <row r="366" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A366" s="3" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="B366" s="3" t="s">
         <v>1068</v>
@@ -75262,7 +75274,7 @@
         <v>2326</v>
       </c>
       <c r="E366" s="3" t="s">
-        <v>1075</v>
+        <v>966</v>
       </c>
       <c r="F366" s="3" t="s">
         <v>333</v>
@@ -75271,10 +75283,10 @@
         <v>7</v>
       </c>
       <c r="H366" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I366" s="4" t="s">
-        <v>2326</v>
+        <v>16</v>
       </c>
       <c r="J366" s="3" t="s">
         <v>333</v>
@@ -75289,7 +75301,7 @@
     </row>
     <row r="367" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A367" s="3" t="s">
-        <v>1163</v>
+        <v>1168</v>
       </c>
       <c r="B367" s="3" t="s">
         <v>1068</v>
@@ -75301,7 +75313,7 @@
         <v>2327</v>
       </c>
       <c r="E367" s="3" t="s">
-        <v>837</v>
+        <v>968</v>
       </c>
       <c r="F367" s="3" t="s">
         <v>333</v>
@@ -75328,7 +75340,7 @@
     </row>
     <row r="368" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A368" s="3" t="s">
-        <v>1164</v>
+        <v>1157</v>
       </c>
       <c r="B368" s="3" t="s">
         <v>1068</v>
@@ -75340,7 +75352,7 @@
         <v>2328</v>
       </c>
       <c r="E368" s="3" t="s">
-        <v>966</v>
+        <v>815</v>
       </c>
       <c r="F368" s="3" t="s">
         <v>333</v>
@@ -75367,7 +75379,7 @@
     </row>
     <row r="369" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A369" s="3" t="s">
-        <v>1168</v>
+        <v>1159</v>
       </c>
       <c r="B369" s="3" t="s">
         <v>1068</v>
@@ -75379,7 +75391,7 @@
         <v>2329</v>
       </c>
       <c r="E369" s="3" t="s">
-        <v>968</v>
+        <v>810</v>
       </c>
       <c r="F369" s="3" t="s">
         <v>333</v>
@@ -75406,7 +75418,7 @@
     </row>
     <row r="370" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A370" s="3" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="B370" s="3" t="s">
         <v>1068</v>
@@ -75418,7 +75430,7 @@
         <v>2330</v>
       </c>
       <c r="E370" s="3" t="s">
-        <v>815</v>
+        <v>1075</v>
       </c>
       <c r="F370" s="3" t="s">
         <v>333</v>
@@ -75445,7 +75457,7 @@
     </row>
     <row r="371" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A371" s="3" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="B371" s="3" t="s">
         <v>1068</v>
@@ -75457,7 +75469,7 @@
         <v>2331</v>
       </c>
       <c r="E371" s="3" t="s">
-        <v>810</v>
+        <v>837</v>
       </c>
       <c r="F371" s="3" t="s">
         <v>333</v>
@@ -75484,7 +75496,7 @@
     </row>
     <row r="372" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A372" s="3" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="B372" s="3" t="s">
         <v>1068</v>
@@ -75496,7 +75508,7 @@
         <v>2332</v>
       </c>
       <c r="E372" s="3" t="s">
-        <v>1075</v>
+        <v>966</v>
       </c>
       <c r="F372" s="3" t="s">
         <v>333</v>
@@ -75523,7 +75535,7 @@
     </row>
     <row r="373" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A373" s="3" t="s">
-        <v>1163</v>
+        <v>1168</v>
       </c>
       <c r="B373" s="3" t="s">
         <v>1068</v>
@@ -75535,7 +75547,7 @@
         <v>2333</v>
       </c>
       <c r="E373" s="3" t="s">
-        <v>837</v>
+        <v>968</v>
       </c>
       <c r="F373" s="3" t="s">
         <v>333</v>
@@ -75562,7 +75574,7 @@
     </row>
     <row r="374" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A374" s="3" t="s">
-        <v>1164</v>
+        <v>1157</v>
       </c>
       <c r="B374" s="3" t="s">
         <v>1068</v>
@@ -75574,7 +75586,7 @@
         <v>2334</v>
       </c>
       <c r="E374" s="3" t="s">
-        <v>966</v>
+        <v>815</v>
       </c>
       <c r="F374" s="3" t="s">
         <v>333</v>
@@ -75601,7 +75613,7 @@
     </row>
     <row r="375" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A375" s="3" t="s">
-        <v>1168</v>
+        <v>1159</v>
       </c>
       <c r="B375" s="3" t="s">
         <v>1068</v>
@@ -75613,7 +75625,7 @@
         <v>2335</v>
       </c>
       <c r="E375" s="3" t="s">
-        <v>968</v>
+        <v>810</v>
       </c>
       <c r="F375" s="3" t="s">
         <v>333</v>
@@ -75622,10 +75634,10 @@
         <v>7</v>
       </c>
       <c r="H375" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I375" s="4" t="s">
-        <v>16</v>
+        <v>2335</v>
       </c>
       <c r="J375" s="3" t="s">
         <v>333</v>
@@ -75640,7 +75652,7 @@
     </row>
     <row r="376" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A376" s="3" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="B376" s="3" t="s">
         <v>1068</v>
@@ -75652,7 +75664,7 @@
         <v>2336</v>
       </c>
       <c r="E376" s="3" t="s">
-        <v>815</v>
+        <v>1075</v>
       </c>
       <c r="F376" s="3" t="s">
         <v>333</v>
@@ -75661,10 +75673,10 @@
         <v>7</v>
       </c>
       <c r="H376" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I376" s="4" t="s">
-        <v>16</v>
+        <v>2336</v>
       </c>
       <c r="J376" s="3" t="s">
         <v>333</v>
@@ -75679,7 +75691,7 @@
     </row>
     <row r="377" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A377" s="3" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="B377" s="3" t="s">
         <v>1068</v>
@@ -75691,7 +75703,7 @@
         <v>2337</v>
       </c>
       <c r="E377" s="3" t="s">
-        <v>810</v>
+        <v>837</v>
       </c>
       <c r="F377" s="3" t="s">
         <v>333</v>
@@ -75700,10 +75712,10 @@
         <v>7</v>
       </c>
       <c r="H377" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I377" s="4" t="s">
-        <v>16</v>
+        <v>2337</v>
       </c>
       <c r="J377" s="3" t="s">
         <v>333</v>
@@ -75718,7 +75730,7 @@
     </row>
     <row r="378" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A378" s="3" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="B378" s="3" t="s">
         <v>1068</v>
@@ -75730,7 +75742,7 @@
         <v>2338</v>
       </c>
       <c r="E378" s="3" t="s">
-        <v>1075</v>
+        <v>966</v>
       </c>
       <c r="F378" s="3" t="s">
         <v>333</v>
@@ -75739,10 +75751,10 @@
         <v>7</v>
       </c>
       <c r="H378" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I378" s="4" t="s">
-        <v>16</v>
+        <v>2338</v>
       </c>
       <c r="J378" s="3" t="s">
         <v>333</v>
@@ -75757,7 +75769,7 @@
     </row>
     <row r="379" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A379" s="3" t="s">
-        <v>1163</v>
+        <v>1168</v>
       </c>
       <c r="B379" s="3" t="s">
         <v>1068</v>
@@ -75769,7 +75781,7 @@
         <v>2339</v>
       </c>
       <c r="E379" s="3" t="s">
-        <v>837</v>
+        <v>968</v>
       </c>
       <c r="F379" s="3" t="s">
         <v>333</v>
@@ -75796,7 +75808,7 @@
     </row>
     <row r="380" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A380" s="3" t="s">
-        <v>1164</v>
+        <v>1157</v>
       </c>
       <c r="B380" s="3" t="s">
         <v>1068</v>
@@ -75808,7 +75820,7 @@
         <v>2340</v>
       </c>
       <c r="E380" s="3" t="s">
-        <v>966</v>
+        <v>815</v>
       </c>
       <c r="F380" s="3" t="s">
         <v>333</v>
@@ -75835,7 +75847,7 @@
     </row>
     <row r="381" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A381" s="3" t="s">
-        <v>1168</v>
+        <v>1159</v>
       </c>
       <c r="B381" s="3" t="s">
         <v>1068</v>
@@ -75847,7 +75859,7 @@
         <v>2341</v>
       </c>
       <c r="E381" s="3" t="s">
-        <v>968</v>
+        <v>810</v>
       </c>
       <c r="F381" s="3" t="s">
         <v>333</v>
@@ -75856,10 +75868,10 @@
         <v>7</v>
       </c>
       <c r="H381" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I381" s="4" t="s">
-        <v>2341</v>
+        <v>16</v>
       </c>
       <c r="J381" s="3" t="s">
         <v>333</v>
@@ -75874,7 +75886,7 @@
     </row>
     <row r="382" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A382" s="3" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="B382" s="3" t="s">
         <v>1068</v>
@@ -75886,7 +75898,7 @@
         <v>2342</v>
       </c>
       <c r="E382" s="3" t="s">
-        <v>815</v>
+        <v>1075</v>
       </c>
       <c r="F382" s="3" t="s">
         <v>333</v>
@@ -75895,10 +75907,10 @@
         <v>7</v>
       </c>
       <c r="H382" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I382" s="4" t="s">
-        <v>2342</v>
+        <v>16</v>
       </c>
       <c r="J382" s="3" t="s">
         <v>333</v>
@@ -75913,7 +75925,7 @@
     </row>
     <row r="383" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A383" s="3" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="B383" s="3" t="s">
         <v>1068</v>
@@ -75925,7 +75937,7 @@
         <v>2343</v>
       </c>
       <c r="E383" s="3" t="s">
-        <v>810</v>
+        <v>837</v>
       </c>
       <c r="F383" s="3" t="s">
         <v>333</v>
@@ -75934,10 +75946,10 @@
         <v>7</v>
       </c>
       <c r="H383" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I383" s="4" t="s">
-        <v>2343</v>
+        <v>16</v>
       </c>
       <c r="J383" s="3" t="s">
         <v>333</v>
@@ -75952,7 +75964,7 @@
     </row>
     <row r="384" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A384" s="3" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="B384" s="3" t="s">
         <v>1068</v>
@@ -75964,7 +75976,7 @@
         <v>2344</v>
       </c>
       <c r="E384" s="3" t="s">
-        <v>1075</v>
+        <v>966</v>
       </c>
       <c r="F384" s="3" t="s">
         <v>333</v>
@@ -75973,10 +75985,10 @@
         <v>7</v>
       </c>
       <c r="H384" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I384" s="4" t="s">
-        <v>2344</v>
+        <v>16</v>
       </c>
       <c r="J384" s="3" t="s">
         <v>333</v>
@@ -75991,7 +76003,7 @@
     </row>
     <row r="385" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A385" s="3" t="s">
-        <v>1163</v>
+        <v>1168</v>
       </c>
       <c r="B385" s="3" t="s">
         <v>1068</v>
@@ -76003,7 +76015,7 @@
         <v>2345</v>
       </c>
       <c r="E385" s="3" t="s">
-        <v>837</v>
+        <v>968</v>
       </c>
       <c r="F385" s="3" t="s">
         <v>333</v>
@@ -76030,7 +76042,7 @@
     </row>
     <row r="386" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A386" s="3" t="s">
-        <v>1164</v>
+        <v>1157</v>
       </c>
       <c r="B386" s="3" t="s">
         <v>1068</v>
@@ -76042,7 +76054,7 @@
         <v>2346</v>
       </c>
       <c r="E386" s="3" t="s">
-        <v>966</v>
+        <v>815</v>
       </c>
       <c r="F386" s="3" t="s">
         <v>333</v>
@@ -76069,7 +76081,7 @@
     </row>
     <row r="387" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A387" s="3" t="s">
-        <v>1168</v>
+        <v>1159</v>
       </c>
       <c r="B387" s="3" t="s">
         <v>1068</v>
@@ -76081,7 +76093,7 @@
         <v>2347</v>
       </c>
       <c r="E387" s="3" t="s">
-        <v>968</v>
+        <v>810</v>
       </c>
       <c r="F387" s="3" t="s">
         <v>333</v>
@@ -76090,10 +76102,10 @@
         <v>7</v>
       </c>
       <c r="H387" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I387" s="4" t="s">
-        <v>16</v>
+        <v>2347</v>
       </c>
       <c r="J387" s="3" t="s">
         <v>333</v>
@@ -76108,7 +76120,7 @@
     </row>
     <row r="388" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A388" s="3" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="B388" s="3" t="s">
         <v>1068</v>
@@ -76120,7 +76132,7 @@
         <v>2348</v>
       </c>
       <c r="E388" s="3" t="s">
-        <v>815</v>
+        <v>1075</v>
       </c>
       <c r="F388" s="3" t="s">
         <v>333</v>
@@ -76129,10 +76141,10 @@
         <v>7</v>
       </c>
       <c r="H388" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I388" s="4" t="s">
-        <v>16</v>
+        <v>2348</v>
       </c>
       <c r="J388" s="3" t="s">
         <v>333</v>
@@ -76147,7 +76159,7 @@
     </row>
     <row r="389" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A389" s="3" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="B389" s="3" t="s">
         <v>1068</v>
@@ -76159,7 +76171,7 @@
         <v>2349</v>
       </c>
       <c r="E389" s="3" t="s">
-        <v>810</v>
+        <v>837</v>
       </c>
       <c r="F389" s="3" t="s">
         <v>333</v>
@@ -76168,10 +76180,10 @@
         <v>7</v>
       </c>
       <c r="H389" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I389" s="4" t="s">
-        <v>16</v>
+        <v>2349</v>
       </c>
       <c r="J389" s="3" t="s">
         <v>333</v>
@@ -76186,7 +76198,7 @@
     </row>
     <row r="390" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A390" s="3" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="B390" s="3" t="s">
         <v>1068</v>
@@ -76198,7 +76210,7 @@
         <v>2350</v>
       </c>
       <c r="E390" s="3" t="s">
-        <v>1075</v>
+        <v>966</v>
       </c>
       <c r="F390" s="3" t="s">
         <v>333</v>
@@ -76207,10 +76219,10 @@
         <v>7</v>
       </c>
       <c r="H390" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I390" s="4" t="s">
-        <v>16</v>
+        <v>2350</v>
       </c>
       <c r="J390" s="3" t="s">
         <v>333</v>
@@ -76225,7 +76237,7 @@
     </row>
     <row r="391" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A391" s="3" t="s">
-        <v>1163</v>
+        <v>1168</v>
       </c>
       <c r="B391" s="3" t="s">
         <v>1068</v>
@@ -76237,7 +76249,7 @@
         <v>2351</v>
       </c>
       <c r="E391" s="3" t="s">
-        <v>837</v>
+        <v>968</v>
       </c>
       <c r="F391" s="3" t="s">
         <v>333</v>
@@ -76264,7 +76276,7 @@
     </row>
     <row r="392" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A392" s="3" t="s">
-        <v>1164</v>
+        <v>1157</v>
       </c>
       <c r="B392" s="3" t="s">
         <v>1068</v>
@@ -76276,7 +76288,7 @@
         <v>2352</v>
       </c>
       <c r="E392" s="3" t="s">
-        <v>966</v>
+        <v>815</v>
       </c>
       <c r="F392" s="3" t="s">
         <v>333</v>
@@ -76303,7 +76315,7 @@
     </row>
     <row r="393" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A393" s="3" t="s">
-        <v>1083</v>
+        <v>1159</v>
       </c>
       <c r="B393" s="3" t="s">
         <v>1068</v>
@@ -76315,7 +76327,7 @@
         <v>2353</v>
       </c>
       <c r="E393" s="3" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="F393" s="3" t="s">
         <v>333</v>
@@ -76342,7 +76354,7 @@
     </row>
     <row r="394" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A394" s="3" t="s">
-        <v>1085</v>
+        <v>1161</v>
       </c>
       <c r="B394" s="3" t="s">
         <v>1068</v>
@@ -76354,7 +76366,7 @@
         <v>2354</v>
       </c>
       <c r="E394" s="3" t="s">
-        <v>815</v>
+        <v>1075</v>
       </c>
       <c r="F394" s="3" t="s">
         <v>333</v>
@@ -76381,7 +76393,7 @@
     </row>
     <row r="395" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A395" s="3" t="s">
-        <v>1086</v>
+        <v>1163</v>
       </c>
       <c r="B395" s="3" t="s">
         <v>1068</v>
@@ -76393,7 +76405,7 @@
         <v>2355</v>
       </c>
       <c r="E395" s="3" t="s">
-        <v>1087</v>
+        <v>837</v>
       </c>
       <c r="F395" s="3" t="s">
         <v>333</v>
@@ -76420,7 +76432,7 @@
     </row>
     <row r="396" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A396" s="3" t="s">
-        <v>1088</v>
+        <v>1164</v>
       </c>
       <c r="B396" s="3" t="s">
         <v>1068</v>
@@ -76432,7 +76444,7 @@
         <v>2356</v>
       </c>
       <c r="E396" s="3" t="s">
-        <v>810</v>
+        <v>966</v>
       </c>
       <c r="F396" s="3" t="s">
         <v>333</v>
@@ -76459,7 +76471,7 @@
     </row>
     <row r="397" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A397" s="3" t="s">
-        <v>1091</v>
+        <v>1083</v>
       </c>
       <c r="B397" s="3" t="s">
         <v>1068</v>
@@ -76471,7 +76483,7 @@
         <v>2357</v>
       </c>
       <c r="E397" s="3" t="s">
-        <v>1075</v>
+        <v>805</v>
       </c>
       <c r="F397" s="3" t="s">
         <v>333</v>
@@ -76498,7 +76510,7 @@
     </row>
     <row r="398" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A398" s="3" t="s">
-        <v>1094</v>
+        <v>1085</v>
       </c>
       <c r="B398" s="3" t="s">
         <v>1068</v>
@@ -76510,7 +76522,7 @@
         <v>2358</v>
       </c>
       <c r="E398" s="3" t="s">
-        <v>837</v>
+        <v>815</v>
       </c>
       <c r="F398" s="3" t="s">
         <v>333</v>
@@ -76537,7 +76549,7 @@
     </row>
     <row r="399" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A399" s="3" t="s">
-        <v>1095</v>
+        <v>1086</v>
       </c>
       <c r="B399" s="3" t="s">
         <v>1068</v>
@@ -76549,7 +76561,7 @@
         <v>2359</v>
       </c>
       <c r="E399" s="3" t="s">
-        <v>966</v>
+        <v>1087</v>
       </c>
       <c r="F399" s="3" t="s">
         <v>333</v>
@@ -76576,7 +76588,7 @@
     </row>
     <row r="400" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A400" s="3" t="s">
-        <v>1176</v>
+        <v>1088</v>
       </c>
       <c r="B400" s="3" t="s">
         <v>1068</v>
@@ -76588,7 +76600,7 @@
         <v>2360</v>
       </c>
       <c r="E400" s="3" t="s">
-        <v>16</v>
+        <v>810</v>
       </c>
       <c r="F400" s="3" t="s">
         <v>333</v>
@@ -76615,7 +76627,7 @@
     </row>
     <row r="401" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A401" s="3" t="s">
-        <v>1083</v>
+        <v>1091</v>
       </c>
       <c r="B401" s="3" t="s">
         <v>1068</v>
@@ -76627,7 +76639,7 @@
         <v>2361</v>
       </c>
       <c r="E401" s="3" t="s">
-        <v>805</v>
+        <v>1075</v>
       </c>
       <c r="F401" s="3" t="s">
         <v>333</v>
@@ -76654,7 +76666,7 @@
     </row>
     <row r="402" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A402" s="3" t="s">
-        <v>1085</v>
+        <v>1094</v>
       </c>
       <c r="B402" s="3" t="s">
         <v>1068</v>
@@ -76666,7 +76678,7 @@
         <v>2362</v>
       </c>
       <c r="E402" s="3" t="s">
-        <v>815</v>
+        <v>837</v>
       </c>
       <c r="F402" s="3" t="s">
         <v>333</v>
@@ -76693,7 +76705,7 @@
     </row>
     <row r="403" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A403" s="3" t="s">
-        <v>1086</v>
+        <v>1095</v>
       </c>
       <c r="B403" s="3" t="s">
         <v>1068</v>
@@ -76705,7 +76717,7 @@
         <v>2363</v>
       </c>
       <c r="E403" s="3" t="s">
-        <v>1087</v>
+        <v>966</v>
       </c>
       <c r="F403" s="3" t="s">
         <v>333</v>
@@ -76732,7 +76744,7 @@
     </row>
     <row r="404" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A404" s="3" t="s">
-        <v>1088</v>
+        <v>1176</v>
       </c>
       <c r="B404" s="3" t="s">
         <v>1068</v>
@@ -76744,7 +76756,7 @@
         <v>2364</v>
       </c>
       <c r="E404" s="3" t="s">
-        <v>810</v>
+        <v>16</v>
       </c>
       <c r="F404" s="3" t="s">
         <v>333</v>
@@ -76771,7 +76783,7 @@
     </row>
     <row r="405" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A405" s="3" t="s">
-        <v>1091</v>
+        <v>1083</v>
       </c>
       <c r="B405" s="3" t="s">
         <v>1068</v>
@@ -76783,7 +76795,7 @@
         <v>2365</v>
       </c>
       <c r="E405" s="3" t="s">
-        <v>1075</v>
+        <v>805</v>
       </c>
       <c r="F405" s="3" t="s">
         <v>333</v>
@@ -76810,7 +76822,7 @@
     </row>
     <row r="406" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A406" s="3" t="s">
-        <v>1094</v>
+        <v>1085</v>
       </c>
       <c r="B406" s="3" t="s">
         <v>1068</v>
@@ -76822,7 +76834,7 @@
         <v>2366</v>
       </c>
       <c r="E406" s="3" t="s">
-        <v>837</v>
+        <v>815</v>
       </c>
       <c r="F406" s="3" t="s">
         <v>333</v>
@@ -76849,7 +76861,7 @@
     </row>
     <row r="407" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A407" s="3" t="s">
-        <v>1095</v>
+        <v>1086</v>
       </c>
       <c r="B407" s="3" t="s">
         <v>1068</v>
@@ -76861,7 +76873,7 @@
         <v>2367</v>
       </c>
       <c r="E407" s="3" t="s">
-        <v>966</v>
+        <v>1087</v>
       </c>
       <c r="F407" s="3" t="s">
         <v>333</v>
@@ -76888,7 +76900,7 @@
     </row>
     <row r="408" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A408" s="3" t="s">
-        <v>1083</v>
+        <v>1088</v>
       </c>
       <c r="B408" s="3" t="s">
         <v>1068</v>
@@ -76900,7 +76912,7 @@
         <v>2368</v>
       </c>
       <c r="E408" s="3" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="F408" s="3" t="s">
         <v>333</v>
@@ -76927,7 +76939,7 @@
     </row>
     <row r="409" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A409" s="3" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="B409" s="3" t="s">
         <v>1068</v>
@@ -76939,7 +76951,7 @@
         <v>2369</v>
       </c>
       <c r="E409" s="3" t="s">
-        <v>815</v>
+        <v>1075</v>
       </c>
       <c r="F409" s="3" t="s">
         <v>333</v>
@@ -76966,7 +76978,7 @@
     </row>
     <row r="410" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A410" s="3" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
       <c r="B410" s="3" t="s">
         <v>1068</v>
@@ -76978,7 +76990,7 @@
         <v>2370</v>
       </c>
       <c r="E410" s="3" t="s">
-        <v>1087</v>
+        <v>837</v>
       </c>
       <c r="F410" s="3" t="s">
         <v>333</v>
@@ -77005,7 +77017,7 @@
     </row>
     <row r="411" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A411" s="3" t="s">
-        <v>1088</v>
+        <v>1095</v>
       </c>
       <c r="B411" s="3" t="s">
         <v>1068</v>
@@ -77017,7 +77029,7 @@
         <v>2371</v>
       </c>
       <c r="E411" s="3" t="s">
-        <v>810</v>
+        <v>966</v>
       </c>
       <c r="F411" s="3" t="s">
         <v>333</v>
@@ -77044,7 +77056,7 @@
     </row>
     <row r="412" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A412" s="3" t="s">
-        <v>1091</v>
+        <v>1083</v>
       </c>
       <c r="B412" s="3" t="s">
         <v>1068</v>
@@ -77056,7 +77068,7 @@
         <v>2372</v>
       </c>
       <c r="E412" s="3" t="s">
-        <v>1075</v>
+        <v>805</v>
       </c>
       <c r="F412" s="3" t="s">
         <v>333</v>
@@ -77083,7 +77095,7 @@
     </row>
     <row r="413" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A413" s="3" t="s">
-        <v>1094</v>
+        <v>1085</v>
       </c>
       <c r="B413" s="3" t="s">
         <v>1068</v>
@@ -77095,7 +77107,7 @@
         <v>2373</v>
       </c>
       <c r="E413" s="3" t="s">
-        <v>837</v>
+        <v>815</v>
       </c>
       <c r="F413" s="3" t="s">
         <v>333</v>
@@ -77122,7 +77134,7 @@
     </row>
     <row r="414" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A414" s="3" t="s">
-        <v>1095</v>
+        <v>1086</v>
       </c>
       <c r="B414" s="3" t="s">
         <v>1068</v>
@@ -77134,7 +77146,7 @@
         <v>2374</v>
       </c>
       <c r="E414" s="3" t="s">
-        <v>966</v>
+        <v>1087</v>
       </c>
       <c r="F414" s="3" t="s">
         <v>333</v>
@@ -77161,7 +77173,7 @@
     </row>
     <row r="415" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A415" s="3" t="s">
-        <v>1083</v>
+        <v>1088</v>
       </c>
       <c r="B415" s="3" t="s">
         <v>1068</v>
@@ -77173,7 +77185,7 @@
         <v>2375</v>
       </c>
       <c r="E415" s="3" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="F415" s="3" t="s">
         <v>333</v>
@@ -77182,10 +77194,10 @@
         <v>7</v>
       </c>
       <c r="H415" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I415" s="4" t="s">
-        <v>2375</v>
+        <v>16</v>
       </c>
       <c r="J415" s="3" t="s">
         <v>333</v>
@@ -77200,7 +77212,7 @@
     </row>
     <row r="416" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A416" s="3" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="B416" s="3" t="s">
         <v>1068</v>
@@ -77212,7 +77224,7 @@
         <v>2376</v>
       </c>
       <c r="E416" s="3" t="s">
-        <v>815</v>
+        <v>1075</v>
       </c>
       <c r="F416" s="3" t="s">
         <v>333</v>
@@ -77221,10 +77233,10 @@
         <v>7</v>
       </c>
       <c r="H416" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I416" s="4" t="s">
-        <v>2376</v>
+        <v>16</v>
       </c>
       <c r="J416" s="3" t="s">
         <v>333</v>
@@ -77239,7 +77251,7 @@
     </row>
     <row r="417" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A417" s="3" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
       <c r="B417" s="3" t="s">
         <v>1068</v>
@@ -77251,7 +77263,7 @@
         <v>2377</v>
       </c>
       <c r="E417" s="3" t="s">
-        <v>1087</v>
+        <v>837</v>
       </c>
       <c r="F417" s="3" t="s">
         <v>333</v>
@@ -77260,10 +77272,10 @@
         <v>7</v>
       </c>
       <c r="H417" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I417" s="4" t="s">
-        <v>2377</v>
+        <v>16</v>
       </c>
       <c r="J417" s="3" t="s">
         <v>333</v>
@@ -77278,7 +77290,7 @@
     </row>
     <row r="418" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A418" s="3" t="s">
-        <v>1088</v>
+        <v>1095</v>
       </c>
       <c r="B418" s="3" t="s">
         <v>1068</v>
@@ -77290,7 +77302,7 @@
         <v>2378</v>
       </c>
       <c r="E418" s="3" t="s">
-        <v>810</v>
+        <v>966</v>
       </c>
       <c r="F418" s="3" t="s">
         <v>333</v>
@@ -77299,10 +77311,10 @@
         <v>7</v>
       </c>
       <c r="H418" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I418" s="4" t="s">
-        <v>2378</v>
+        <v>16</v>
       </c>
       <c r="J418" s="3" t="s">
         <v>333</v>
@@ -77317,7 +77329,7 @@
     </row>
     <row r="419" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A419" s="3" t="s">
-        <v>1091</v>
+        <v>1083</v>
       </c>
       <c r="B419" s="3" t="s">
         <v>1068</v>
@@ -77329,7 +77341,7 @@
         <v>2379</v>
       </c>
       <c r="E419" s="3" t="s">
-        <v>1075</v>
+        <v>805</v>
       </c>
       <c r="F419" s="3" t="s">
         <v>333</v>
@@ -77356,7 +77368,7 @@
     </row>
     <row r="420" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A420" s="3" t="s">
-        <v>1094</v>
+        <v>1085</v>
       </c>
       <c r="B420" s="3" t="s">
         <v>1068</v>
@@ -77368,7 +77380,7 @@
         <v>2380</v>
       </c>
       <c r="E420" s="3" t="s">
-        <v>837</v>
+        <v>815</v>
       </c>
       <c r="F420" s="3" t="s">
         <v>333</v>
@@ -77395,7 +77407,7 @@
     </row>
     <row r="421" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A421" s="3" t="s">
-        <v>1095</v>
+        <v>1086</v>
       </c>
       <c r="B421" s="3" t="s">
         <v>1068</v>
@@ -77407,7 +77419,7 @@
         <v>2381</v>
       </c>
       <c r="E421" s="3" t="s">
-        <v>966</v>
+        <v>1087</v>
       </c>
       <c r="F421" s="3" t="s">
         <v>333</v>
@@ -77434,7 +77446,7 @@
     </row>
     <row r="422" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A422" s="3" t="s">
-        <v>1176</v>
+        <v>1088</v>
       </c>
       <c r="B422" s="3" t="s">
         <v>1068</v>
@@ -77446,7 +77458,7 @@
         <v>2382</v>
       </c>
       <c r="E422" s="3" t="s">
-        <v>16</v>
+        <v>810</v>
       </c>
       <c r="F422" s="3" t="s">
         <v>333</v>
@@ -77458,7 +77470,7 @@
         <v>18</v>
       </c>
       <c r="I422" s="4" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="J422" s="3" t="s">
         <v>333</v>
@@ -77473,19 +77485,19 @@
     </row>
     <row r="423" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A423" s="3" t="s">
-        <v>1083</v>
+        <v>1091</v>
       </c>
       <c r="B423" s="3" t="s">
         <v>1068</v>
       </c>
       <c r="C423" s="3" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="D423" s="4" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="E423" s="3" t="s">
-        <v>805</v>
+        <v>1075</v>
       </c>
       <c r="F423" s="3" t="s">
         <v>333</v>
@@ -77497,7 +77509,7 @@
         <v>18</v>
       </c>
       <c r="I423" s="4" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="J423" s="3" t="s">
         <v>333</v>
@@ -77512,19 +77524,19 @@
     </row>
     <row r="424" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A424" s="3" t="s">
-        <v>1085</v>
+        <v>1094</v>
       </c>
       <c r="B424" s="3" t="s">
         <v>1068</v>
       </c>
       <c r="C424" s="3" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="D424" s="4" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="E424" s="3" t="s">
-        <v>815</v>
+        <v>837</v>
       </c>
       <c r="F424" s="3" t="s">
         <v>333</v>
@@ -77536,7 +77548,7 @@
         <v>18</v>
       </c>
       <c r="I424" s="4" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="J424" s="3" t="s">
         <v>333</v>
@@ -77551,19 +77563,19 @@
     </row>
     <row r="425" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A425" s="3" t="s">
-        <v>1086</v>
+        <v>1095</v>
       </c>
       <c r="B425" s="3" t="s">
         <v>1068</v>
       </c>
       <c r="C425" s="3" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="D425" s="4" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="E425" s="3" t="s">
-        <v>1087</v>
+        <v>966</v>
       </c>
       <c r="F425" s="3" t="s">
         <v>333</v>
@@ -77575,7 +77587,7 @@
         <v>18</v>
       </c>
       <c r="I425" s="4" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="J425" s="3" t="s">
         <v>333</v>
@@ -77590,19 +77602,19 @@
     </row>
     <row r="426" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A426" s="3" t="s">
-        <v>1088</v>
+        <v>1176</v>
       </c>
       <c r="B426" s="3" t="s">
         <v>1068</v>
       </c>
       <c r="C426" s="3" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="D426" s="4" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="E426" s="3" t="s">
-        <v>810</v>
+        <v>16</v>
       </c>
       <c r="F426" s="3" t="s">
         <v>333</v>
@@ -77629,7 +77641,7 @@
     </row>
     <row r="427" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A427" s="3" t="s">
-        <v>1091</v>
+        <v>1083</v>
       </c>
       <c r="B427" s="3" t="s">
         <v>1068</v>
@@ -77641,7 +77653,7 @@
         <v>2388</v>
       </c>
       <c r="E427" s="3" t="s">
-        <v>1075</v>
+        <v>805</v>
       </c>
       <c r="F427" s="3" t="s">
         <v>333</v>
@@ -77668,7 +77680,7 @@
     </row>
     <row r="428" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A428" s="3" t="s">
-        <v>1094</v>
+        <v>1085</v>
       </c>
       <c r="B428" s="3" t="s">
         <v>1068</v>
@@ -77680,7 +77692,7 @@
         <v>2389</v>
       </c>
       <c r="E428" s="3" t="s">
-        <v>837</v>
+        <v>815</v>
       </c>
       <c r="F428" s="3" t="s">
         <v>333</v>
@@ -77707,7 +77719,7 @@
     </row>
     <row r="429" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A429" s="3" t="s">
-        <v>1095</v>
+        <v>1086</v>
       </c>
       <c r="B429" s="3" t="s">
         <v>1068</v>
@@ -77719,7 +77731,7 @@
         <v>2390</v>
       </c>
       <c r="E429" s="3" t="s">
-        <v>966</v>
+        <v>1087</v>
       </c>
       <c r="F429" s="3" t="s">
         <v>333</v>
@@ -77746,7 +77758,7 @@
     </row>
     <row r="430" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A430" s="3" t="s">
-        <v>1176</v>
+        <v>1088</v>
       </c>
       <c r="B430" s="3" t="s">
         <v>1068</v>
@@ -77758,7 +77770,7 @@
         <v>2391</v>
       </c>
       <c r="E430" s="3" t="s">
-        <v>16</v>
+        <v>810</v>
       </c>
       <c r="F430" s="3" t="s">
         <v>333</v>
@@ -77770,7 +77782,7 @@
         <v>18</v>
       </c>
       <c r="I430" s="4" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="J430" s="3" t="s">
         <v>333</v>
@@ -77785,19 +77797,19 @@
     </row>
     <row r="431" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A431" s="3" t="s">
-        <v>1083</v>
+        <v>1091</v>
       </c>
       <c r="B431" s="3" t="s">
         <v>1068</v>
       </c>
       <c r="C431" s="3" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="D431" s="4" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="E431" s="3" t="s">
-        <v>805</v>
+        <v>1075</v>
       </c>
       <c r="F431" s="3" t="s">
         <v>333</v>
@@ -77809,7 +77821,7 @@
         <v>18</v>
       </c>
       <c r="I431" s="4" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="J431" s="3" t="s">
         <v>333</v>
@@ -77824,19 +77836,19 @@
     </row>
     <row r="432" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A432" s="3" t="s">
-        <v>1085</v>
+        <v>1094</v>
       </c>
       <c r="B432" s="3" t="s">
         <v>1068</v>
       </c>
       <c r="C432" s="3" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="D432" s="4" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="E432" s="3" t="s">
-        <v>815</v>
+        <v>837</v>
       </c>
       <c r="F432" s="3" t="s">
         <v>333</v>
@@ -77848,7 +77860,7 @@
         <v>18</v>
       </c>
       <c r="I432" s="4" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="J432" s="3" t="s">
         <v>333</v>
@@ -77863,19 +77875,19 @@
     </row>
     <row r="433" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A433" s="3" t="s">
-        <v>1086</v>
+        <v>1095</v>
       </c>
       <c r="B433" s="3" t="s">
         <v>1068</v>
       </c>
       <c r="C433" s="3" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="D433" s="4" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="E433" s="3" t="s">
-        <v>1087</v>
+        <v>966</v>
       </c>
       <c r="F433" s="3" t="s">
         <v>333</v>
@@ -77887,7 +77899,7 @@
         <v>18</v>
       </c>
       <c r="I433" s="4" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="J433" s="3" t="s">
         <v>333</v>
@@ -77902,19 +77914,19 @@
     </row>
     <row r="434" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A434" s="3" t="s">
-        <v>1088</v>
+        <v>1176</v>
       </c>
       <c r="B434" s="3" t="s">
         <v>1068</v>
       </c>
       <c r="C434" s="3" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="D434" s="4" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="E434" s="3" t="s">
-        <v>810</v>
+        <v>16</v>
       </c>
       <c r="F434" s="3" t="s">
         <v>333</v>
@@ -77941,7 +77953,7 @@
     </row>
     <row r="435" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A435" s="3" t="s">
-        <v>1091</v>
+        <v>1083</v>
       </c>
       <c r="B435" s="3" t="s">
         <v>1068</v>
@@ -77953,7 +77965,7 @@
         <v>2397</v>
       </c>
       <c r="E435" s="3" t="s">
-        <v>1075</v>
+        <v>805</v>
       </c>
       <c r="F435" s="3" t="s">
         <v>333</v>
@@ -77980,7 +77992,7 @@
     </row>
     <row r="436" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A436" s="3" t="s">
-        <v>1094</v>
+        <v>1085</v>
       </c>
       <c r="B436" s="3" t="s">
         <v>1068</v>
@@ -77992,7 +78004,7 @@
         <v>2398</v>
       </c>
       <c r="E436" s="3" t="s">
-        <v>837</v>
+        <v>815</v>
       </c>
       <c r="F436" s="3" t="s">
         <v>333</v>
@@ -78019,7 +78031,7 @@
     </row>
     <row r="437" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A437" s="3" t="s">
-        <v>1095</v>
+        <v>1086</v>
       </c>
       <c r="B437" s="3" t="s">
         <v>1068</v>
@@ -78031,7 +78043,7 @@
         <v>2399</v>
       </c>
       <c r="E437" s="3" t="s">
-        <v>966</v>
+        <v>1087</v>
       </c>
       <c r="F437" s="3" t="s">
         <v>333</v>
@@ -78058,7 +78070,7 @@
     </row>
     <row r="438" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A438" s="3" t="s">
-        <v>1083</v>
+        <v>1088</v>
       </c>
       <c r="B438" s="3" t="s">
         <v>1068</v>
@@ -78070,7 +78082,7 @@
         <v>2400</v>
       </c>
       <c r="E438" s="3" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="F438" s="3" t="s">
         <v>333</v>
@@ -78097,7 +78109,7 @@
     </row>
     <row r="439" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A439" s="3" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="B439" s="3" t="s">
         <v>1068</v>
@@ -78109,7 +78121,7 @@
         <v>2401</v>
       </c>
       <c r="E439" s="3" t="s">
-        <v>815</v>
+        <v>1075</v>
       </c>
       <c r="F439" s="3" t="s">
         <v>333</v>
@@ -78136,7 +78148,7 @@
     </row>
     <row r="440" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A440" s="3" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
       <c r="B440" s="3" t="s">
         <v>1068</v>
@@ -78148,7 +78160,7 @@
         <v>2402</v>
       </c>
       <c r="E440" s="3" t="s">
-        <v>1087</v>
+        <v>837</v>
       </c>
       <c r="F440" s="3" t="s">
         <v>333</v>
@@ -78175,7 +78187,7 @@
     </row>
     <row r="441" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A441" s="3" t="s">
-        <v>1088</v>
+        <v>1095</v>
       </c>
       <c r="B441" s="3" t="s">
         <v>1068</v>
@@ -78187,7 +78199,7 @@
         <v>2403</v>
       </c>
       <c r="E441" s="3" t="s">
-        <v>810</v>
+        <v>966</v>
       </c>
       <c r="F441" s="3" t="s">
         <v>333</v>
@@ -78214,7 +78226,7 @@
     </row>
     <row r="442" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A442" s="3" t="s">
-        <v>1091</v>
+        <v>1083</v>
       </c>
       <c r="B442" s="3" t="s">
         <v>1068</v>
@@ -78226,7 +78238,7 @@
         <v>2404</v>
       </c>
       <c r="E442" s="3" t="s">
-        <v>1075</v>
+        <v>805</v>
       </c>
       <c r="F442" s="3" t="s">
         <v>333</v>
@@ -78253,7 +78265,7 @@
     </row>
     <row r="443" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A443" s="3" t="s">
-        <v>1094</v>
+        <v>1085</v>
       </c>
       <c r="B443" s="3" t="s">
         <v>1068</v>
@@ -78265,7 +78277,7 @@
         <v>2405</v>
       </c>
       <c r="E443" s="3" t="s">
-        <v>837</v>
+        <v>815</v>
       </c>
       <c r="F443" s="3" t="s">
         <v>333</v>
@@ -78292,7 +78304,7 @@
     </row>
     <row r="444" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A444" s="3" t="s">
-        <v>1095</v>
+        <v>1086</v>
       </c>
       <c r="B444" s="3" t="s">
         <v>1068</v>
@@ -78304,7 +78316,7 @@
         <v>2406</v>
       </c>
       <c r="E444" s="3" t="s">
-        <v>966</v>
+        <v>1087</v>
       </c>
       <c r="F444" s="3" t="s">
         <v>333</v>
@@ -78331,7 +78343,7 @@
     </row>
     <row r="445" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A445" s="3" t="s">
-        <v>1083</v>
+        <v>1088</v>
       </c>
       <c r="B445" s="3" t="s">
         <v>1068</v>
@@ -78343,7 +78355,7 @@
         <v>2407</v>
       </c>
       <c r="E445" s="3" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="F445" s="3" t="s">
         <v>333</v>
@@ -78352,10 +78364,10 @@
         <v>7</v>
       </c>
       <c r="H445" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I445" s="4" t="s">
-        <v>16</v>
+        <v>2407</v>
       </c>
       <c r="J445" s="3" t="s">
         <v>333</v>
@@ -78370,7 +78382,7 @@
     </row>
     <row r="446" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A446" s="3" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="B446" s="3" t="s">
         <v>1068</v>
@@ -78382,7 +78394,7 @@
         <v>2408</v>
       </c>
       <c r="E446" s="3" t="s">
-        <v>815</v>
+        <v>1075</v>
       </c>
       <c r="F446" s="3" t="s">
         <v>333</v>
@@ -78391,10 +78403,10 @@
         <v>7</v>
       </c>
       <c r="H446" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I446" s="4" t="s">
-        <v>16</v>
+        <v>2408</v>
       </c>
       <c r="J446" s="3" t="s">
         <v>333</v>
@@ -78409,7 +78421,7 @@
     </row>
     <row r="447" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A447" s="3" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
       <c r="B447" s="3" t="s">
         <v>1068</v>
@@ -78421,7 +78433,7 @@
         <v>2409</v>
       </c>
       <c r="E447" s="3" t="s">
-        <v>1087</v>
+        <v>837</v>
       </c>
       <c r="F447" s="3" t="s">
         <v>333</v>
@@ -78430,10 +78442,10 @@
         <v>7</v>
       </c>
       <c r="H447" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I447" s="4" t="s">
-        <v>16</v>
+        <v>2409</v>
       </c>
       <c r="J447" s="3" t="s">
         <v>333</v>
@@ -78448,7 +78460,7 @@
     </row>
     <row r="448" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A448" s="3" t="s">
-        <v>1088</v>
+        <v>1095</v>
       </c>
       <c r="B448" s="3" t="s">
         <v>1068</v>
@@ -78460,7 +78472,7 @@
         <v>2410</v>
       </c>
       <c r="E448" s="3" t="s">
-        <v>810</v>
+        <v>966</v>
       </c>
       <c r="F448" s="3" t="s">
         <v>333</v>
@@ -78469,10 +78481,10 @@
         <v>7</v>
       </c>
       <c r="H448" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I448" s="4" t="s">
-        <v>16</v>
+        <v>2410</v>
       </c>
       <c r="J448" s="3" t="s">
         <v>333</v>
@@ -78487,7 +78499,7 @@
     </row>
     <row r="449" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A449" s="3" t="s">
-        <v>1091</v>
+        <v>1083</v>
       </c>
       <c r="B449" s="3" t="s">
         <v>1068</v>
@@ -78499,7 +78511,7 @@
         <v>2411</v>
       </c>
       <c r="E449" s="3" t="s">
-        <v>1075</v>
+        <v>805</v>
       </c>
       <c r="F449" s="3" t="s">
         <v>333</v>
@@ -78526,7 +78538,7 @@
     </row>
     <row r="450" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A450" s="3" t="s">
-        <v>1094</v>
+        <v>1085</v>
       </c>
       <c r="B450" s="3" t="s">
         <v>1068</v>
@@ -78538,7 +78550,7 @@
         <v>2412</v>
       </c>
       <c r="E450" s="3" t="s">
-        <v>837</v>
+        <v>815</v>
       </c>
       <c r="F450" s="3" t="s">
         <v>333</v>
@@ -78565,7 +78577,7 @@
     </row>
     <row r="451" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A451" s="3" t="s">
-        <v>1095</v>
+        <v>1086</v>
       </c>
       <c r="B451" s="3" t="s">
         <v>1068</v>
@@ -78577,7 +78589,7 @@
         <v>2413</v>
       </c>
       <c r="E451" s="3" t="s">
-        <v>966</v>
+        <v>1087</v>
       </c>
       <c r="F451" s="3" t="s">
         <v>333</v>
@@ -78604,7 +78616,7 @@
     </row>
     <row r="452" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A452" s="3" t="s">
-        <v>1176</v>
+        <v>1088</v>
       </c>
       <c r="B452" s="3" t="s">
         <v>1068</v>
@@ -78616,7 +78628,7 @@
         <v>2414</v>
       </c>
       <c r="E452" s="3" t="s">
-        <v>16</v>
+        <v>810</v>
       </c>
       <c r="F452" s="3" t="s">
         <v>333</v>
@@ -78625,10 +78637,10 @@
         <v>7</v>
       </c>
       <c r="H452" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I452" s="4" t="s">
-        <v>2415</v>
+        <v>16</v>
       </c>
       <c r="J452" s="3" t="s">
         <v>333</v>
@@ -78643,19 +78655,19 @@
     </row>
     <row r="453" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A453" s="3" t="s">
-        <v>1083</v>
+        <v>1091</v>
       </c>
       <c r="B453" s="3" t="s">
         <v>1068</v>
       </c>
       <c r="C453" s="3" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="D453" s="4" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="E453" s="3" t="s">
-        <v>805</v>
+        <v>1075</v>
       </c>
       <c r="F453" s="3" t="s">
         <v>333</v>
@@ -78664,10 +78676,10 @@
         <v>7</v>
       </c>
       <c r="H453" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I453" s="4" t="s">
-        <v>2416</v>
+        <v>16</v>
       </c>
       <c r="J453" s="3" t="s">
         <v>333</v>
@@ -78682,19 +78694,19 @@
     </row>
     <row r="454" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A454" s="3" t="s">
-        <v>1085</v>
+        <v>1094</v>
       </c>
       <c r="B454" s="3" t="s">
         <v>1068</v>
       </c>
       <c r="C454" s="3" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
       <c r="D454" s="4" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
       <c r="E454" s="3" t="s">
-        <v>815</v>
+        <v>837</v>
       </c>
       <c r="F454" s="3" t="s">
         <v>333</v>
@@ -78703,10 +78715,10 @@
         <v>7</v>
       </c>
       <c r="H454" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I454" s="4" t="s">
-        <v>2417</v>
+        <v>16</v>
       </c>
       <c r="J454" s="3" t="s">
         <v>333</v>
@@ -78721,19 +78733,19 @@
     </row>
     <row r="455" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A455" s="3" t="s">
-        <v>1086</v>
+        <v>1095</v>
       </c>
       <c r="B455" s="3" t="s">
         <v>1068</v>
       </c>
       <c r="C455" s="3" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="D455" s="4" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="E455" s="3" t="s">
-        <v>1087</v>
+        <v>966</v>
       </c>
       <c r="F455" s="3" t="s">
         <v>333</v>
@@ -78742,10 +78754,10 @@
         <v>7</v>
       </c>
       <c r="H455" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I455" s="4" t="s">
-        <v>2418</v>
+        <v>16</v>
       </c>
       <c r="J455" s="3" t="s">
         <v>333</v>
@@ -78760,19 +78772,19 @@
     </row>
     <row r="456" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A456" s="3" t="s">
-        <v>1088</v>
+        <v>1176</v>
       </c>
       <c r="B456" s="3" t="s">
         <v>1068</v>
       </c>
       <c r="C456" s="3" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="D456" s="4" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="E456" s="3" t="s">
-        <v>810</v>
+        <v>16</v>
       </c>
       <c r="F456" s="3" t="s">
         <v>333</v>
@@ -78799,7 +78811,7 @@
     </row>
     <row r="457" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A457" s="3" t="s">
-        <v>1091</v>
+        <v>1083</v>
       </c>
       <c r="B457" s="3" t="s">
         <v>1068</v>
@@ -78811,7 +78823,7 @@
         <v>2420</v>
       </c>
       <c r="E457" s="3" t="s">
-        <v>1075</v>
+        <v>805</v>
       </c>
       <c r="F457" s="3" t="s">
         <v>333</v>
@@ -78838,7 +78850,7 @@
     </row>
     <row r="458" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A458" s="3" t="s">
-        <v>1094</v>
+        <v>1085</v>
       </c>
       <c r="B458" s="3" t="s">
         <v>1068</v>
@@ -78850,7 +78862,7 @@
         <v>2421</v>
       </c>
       <c r="E458" s="3" t="s">
-        <v>837</v>
+        <v>815</v>
       </c>
       <c r="F458" s="3" t="s">
         <v>333</v>
@@ -78877,7 +78889,7 @@
     </row>
     <row r="459" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A459" s="3" t="s">
-        <v>1095</v>
+        <v>1086</v>
       </c>
       <c r="B459" s="3" t="s">
         <v>1068</v>
@@ -78889,7 +78901,7 @@
         <v>2422</v>
       </c>
       <c r="E459" s="3" t="s">
-        <v>966</v>
+        <v>1087</v>
       </c>
       <c r="F459" s="3" t="s">
         <v>333</v>
@@ -78916,7 +78928,7 @@
     </row>
     <row r="460" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A460" s="3" t="s">
-        <v>1176</v>
+        <v>1088</v>
       </c>
       <c r="B460" s="3" t="s">
         <v>1068</v>
@@ -78928,7 +78940,7 @@
         <v>2423</v>
       </c>
       <c r="E460" s="3" t="s">
-        <v>16</v>
+        <v>810</v>
       </c>
       <c r="F460" s="3" t="s">
         <v>333</v>
@@ -78940,7 +78952,7 @@
         <v>18</v>
       </c>
       <c r="I460" s="4" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="J460" s="3" t="s">
         <v>333</v>
@@ -78955,19 +78967,19 @@
     </row>
     <row r="461" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A461" s="3" t="s">
-        <v>1083</v>
+        <v>1091</v>
       </c>
       <c r="B461" s="3" t="s">
         <v>1068</v>
       </c>
       <c r="C461" s="3" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="D461" s="4" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="E461" s="3" t="s">
-        <v>805</v>
+        <v>1075</v>
       </c>
       <c r="F461" s="3" t="s">
         <v>333</v>
@@ -78979,7 +78991,7 @@
         <v>18</v>
       </c>
       <c r="I461" s="4" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="J461" s="3" t="s">
         <v>333</v>
@@ -78994,19 +79006,19 @@
     </row>
     <row r="462" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A462" s="3" t="s">
-        <v>1085</v>
+        <v>1094</v>
       </c>
       <c r="B462" s="3" t="s">
         <v>1068</v>
       </c>
       <c r="C462" s="3" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="D462" s="4" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="E462" s="3" t="s">
-        <v>815</v>
+        <v>837</v>
       </c>
       <c r="F462" s="3" t="s">
         <v>333</v>
@@ -79018,7 +79030,7 @@
         <v>18</v>
       </c>
       <c r="I462" s="4" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="J462" s="3" t="s">
         <v>333</v>
@@ -79033,19 +79045,19 @@
     </row>
     <row r="463" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A463" s="3" t="s">
-        <v>1086</v>
+        <v>1095</v>
       </c>
       <c r="B463" s="3" t="s">
         <v>1068</v>
       </c>
       <c r="C463" s="3" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="D463" s="4" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="E463" s="3" t="s">
-        <v>1087</v>
+        <v>966</v>
       </c>
       <c r="F463" s="3" t="s">
         <v>333</v>
@@ -79057,7 +79069,7 @@
         <v>18</v>
       </c>
       <c r="I463" s="4" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="J463" s="3" t="s">
         <v>333</v>
@@ -79072,19 +79084,19 @@
     </row>
     <row r="464" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A464" s="3" t="s">
-        <v>1088</v>
+        <v>1176</v>
       </c>
       <c r="B464" s="3" t="s">
         <v>1068</v>
       </c>
       <c r="C464" s="3" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
       <c r="D464" s="4" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
       <c r="E464" s="3" t="s">
-        <v>810</v>
+        <v>16</v>
       </c>
       <c r="F464" s="3" t="s">
         <v>333</v>
@@ -79111,7 +79123,7 @@
     </row>
     <row r="465" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A465" s="3" t="s">
-        <v>1091</v>
+        <v>1083</v>
       </c>
       <c r="B465" s="3" t="s">
         <v>1068</v>
@@ -79123,7 +79135,7 @@
         <v>2429</v>
       </c>
       <c r="E465" s="3" t="s">
-        <v>1075</v>
+        <v>805</v>
       </c>
       <c r="F465" s="3" t="s">
         <v>333</v>
@@ -79150,7 +79162,7 @@
     </row>
     <row r="466" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A466" s="3" t="s">
-        <v>1094</v>
+        <v>1085</v>
       </c>
       <c r="B466" s="3" t="s">
         <v>1068</v>
@@ -79162,7 +79174,7 @@
         <v>2430</v>
       </c>
       <c r="E466" s="3" t="s">
-        <v>837</v>
+        <v>815</v>
       </c>
       <c r="F466" s="3" t="s">
         <v>333</v>
@@ -79189,7 +79201,7 @@
     </row>
     <row r="467" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A467" s="3" t="s">
-        <v>1095</v>
+        <v>1086</v>
       </c>
       <c r="B467" s="3" t="s">
         <v>1068</v>
@@ -79201,7 +79213,7 @@
         <v>2431</v>
       </c>
       <c r="E467" s="3" t="s">
-        <v>966</v>
+        <v>1087</v>
       </c>
       <c r="F467" s="3" t="s">
         <v>333</v>
@@ -79228,7 +79240,7 @@
     </row>
     <row r="468" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A468" s="3" t="s">
-        <v>1176</v>
+        <v>1088</v>
       </c>
       <c r="B468" s="3" t="s">
         <v>1068</v>
@@ -79240,7 +79252,7 @@
         <v>2432</v>
       </c>
       <c r="E468" s="3" t="s">
-        <v>16</v>
+        <v>810</v>
       </c>
       <c r="F468" s="3" t="s">
         <v>333</v>
@@ -79252,7 +79264,7 @@
         <v>18</v>
       </c>
       <c r="I468" s="4" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="J468" s="3" t="s">
         <v>333</v>
@@ -79267,19 +79279,19 @@
     </row>
     <row r="469" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A469" s="3" t="s">
-        <v>1083</v>
+        <v>1091</v>
       </c>
       <c r="B469" s="3" t="s">
         <v>1068</v>
       </c>
       <c r="C469" s="3" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="D469" s="4" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="E469" s="3" t="s">
-        <v>805</v>
+        <v>1075</v>
       </c>
       <c r="F469" s="3" t="s">
         <v>333</v>
@@ -79288,10 +79300,10 @@
         <v>7</v>
       </c>
       <c r="H469" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I469" s="4" t="s">
-        <v>16</v>
+        <v>2433</v>
       </c>
       <c r="J469" s="3" t="s">
         <v>333</v>
@@ -79306,19 +79318,19 @@
     </row>
     <row r="470" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A470" s="3" t="s">
-        <v>1085</v>
+        <v>1094</v>
       </c>
       <c r="B470" s="3" t="s">
         <v>1068</v>
       </c>
       <c r="C470" s="3" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
       <c r="D470" s="4" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
       <c r="E470" s="3" t="s">
-        <v>815</v>
+        <v>837</v>
       </c>
       <c r="F470" s="3" t="s">
         <v>333</v>
@@ -79327,10 +79339,10 @@
         <v>7</v>
       </c>
       <c r="H470" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I470" s="4" t="s">
-        <v>16</v>
+        <v>2434</v>
       </c>
       <c r="J470" s="3" t="s">
         <v>333</v>
@@ -79345,19 +79357,19 @@
     </row>
     <row r="471" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A471" s="3" t="s">
-        <v>1086</v>
+        <v>1095</v>
       </c>
       <c r="B471" s="3" t="s">
         <v>1068</v>
       </c>
       <c r="C471" s="3" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="D471" s="4" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="E471" s="3" t="s">
-        <v>1087</v>
+        <v>966</v>
       </c>
       <c r="F471" s="3" t="s">
         <v>333</v>
@@ -79366,10 +79378,10 @@
         <v>7</v>
       </c>
       <c r="H471" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I471" s="4" t="s">
-        <v>16</v>
+        <v>2435</v>
       </c>
       <c r="J471" s="3" t="s">
         <v>333</v>
@@ -79384,31 +79396,31 @@
     </row>
     <row r="472" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A472" s="3" t="s">
-        <v>1088</v>
+        <v>1176</v>
       </c>
       <c r="B472" s="3" t="s">
         <v>1068</v>
       </c>
       <c r="C472" s="3" t="s">
+        <v>2436</v>
+      </c>
+      <c r="D472" s="4" t="s">
+        <v>2436</v>
+      </c>
+      <c r="E472" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F472" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="G472" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H472" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I472" s="4" t="s">
         <v>2437</v>
-      </c>
-      <c r="D472" s="4" t="s">
-        <v>2437</v>
-      </c>
-      <c r="E472" s="3" t="s">
-        <v>810</v>
-      </c>
-      <c r="F472" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="G472" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H472" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I472" s="4" t="s">
-        <v>16</v>
       </c>
       <c r="J472" s="3" t="s">
         <v>333</v>
@@ -79423,7 +79435,7 @@
     </row>
     <row r="473" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A473" s="3" t="s">
-        <v>1091</v>
+        <v>1083</v>
       </c>
       <c r="B473" s="3" t="s">
         <v>1068</v>
@@ -79435,7 +79447,7 @@
         <v>2438</v>
       </c>
       <c r="E473" s="3" t="s">
-        <v>1075</v>
+        <v>805</v>
       </c>
       <c r="F473" s="3" t="s">
         <v>333</v>
@@ -79462,7 +79474,7 @@
     </row>
     <row r="474" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A474" s="3" t="s">
-        <v>1094</v>
+        <v>1085</v>
       </c>
       <c r="B474" s="3" t="s">
         <v>1068</v>
@@ -79474,7 +79486,7 @@
         <v>2439</v>
       </c>
       <c r="E474" s="3" t="s">
-        <v>837</v>
+        <v>815</v>
       </c>
       <c r="F474" s="3" t="s">
         <v>333</v>
@@ -79501,7 +79513,7 @@
     </row>
     <row r="475" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A475" s="3" t="s">
-        <v>1095</v>
+        <v>1086</v>
       </c>
       <c r="B475" s="3" t="s">
         <v>1068</v>
@@ -79513,7 +79525,7 @@
         <v>2440</v>
       </c>
       <c r="E475" s="3" t="s">
-        <v>966</v>
+        <v>1087</v>
       </c>
       <c r="F475" s="3" t="s">
         <v>333</v>
@@ -79540,7 +79552,7 @@
     </row>
     <row r="476" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A476" s="3" t="s">
-        <v>1098</v>
+        <v>1088</v>
       </c>
       <c r="B476" s="3" t="s">
         <v>1068</v>
@@ -79552,7 +79564,7 @@
         <v>2441</v>
       </c>
       <c r="E476" s="3" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="F476" s="3" t="s">
         <v>333</v>
@@ -79579,7 +79591,7 @@
     </row>
     <row r="477" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A477" s="3" t="s">
-        <v>1100</v>
+        <v>1091</v>
       </c>
       <c r="B477" s="3" t="s">
         <v>1068</v>
@@ -79591,7 +79603,7 @@
         <v>2442</v>
       </c>
       <c r="E477" s="3" t="s">
-        <v>815</v>
+        <v>1075</v>
       </c>
       <c r="F477" s="3" t="s">
         <v>333</v>
@@ -79618,7 +79630,7 @@
     </row>
     <row r="478" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A478" s="3" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
       <c r="B478" s="3" t="s">
         <v>1068</v>
@@ -79630,7 +79642,7 @@
         <v>2443</v>
       </c>
       <c r="E478" s="3" t="s">
-        <v>805</v>
+        <v>837</v>
       </c>
       <c r="F478" s="3" t="s">
         <v>333</v>
@@ -79639,10 +79651,10 @@
         <v>7</v>
       </c>
       <c r="H478" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I478" s="4" t="s">
-        <v>2443</v>
+        <v>16</v>
       </c>
       <c r="J478" s="3" t="s">
         <v>333</v>
@@ -79657,7 +79669,7 @@
     </row>
     <row r="479" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A479" s="3" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="B479" s="3" t="s">
         <v>1068</v>
@@ -79669,7 +79681,7 @@
         <v>2444</v>
       </c>
       <c r="E479" s="3" t="s">
-        <v>815</v>
+        <v>966</v>
       </c>
       <c r="F479" s="3" t="s">
         <v>333</v>
@@ -79678,10 +79690,10 @@
         <v>7</v>
       </c>
       <c r="H479" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I479" s="4" t="s">
-        <v>2444</v>
+        <v>16</v>
       </c>
       <c r="J479" s="3" t="s">
         <v>333</v>
@@ -79717,10 +79729,10 @@
         <v>7</v>
       </c>
       <c r="H480" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I480" s="4" t="s">
-        <v>2445</v>
+        <v>16</v>
       </c>
       <c r="J480" s="3" t="s">
         <v>333</v>
@@ -79756,10 +79768,10 @@
         <v>7</v>
       </c>
       <c r="H481" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I481" s="4" t="s">
-        <v>2446</v>
+        <v>16</v>
       </c>
       <c r="J481" s="3" t="s">
         <v>333</v>
@@ -80086,7 +80098,7 @@
     </row>
     <row r="490" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A490" s="3" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
       <c r="B490" s="3" t="s">
         <v>1068</v>
@@ -80107,10 +80119,10 @@
         <v>7</v>
       </c>
       <c r="H490" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I490" s="4" t="s">
-        <v>16</v>
+        <v>2455</v>
       </c>
       <c r="J490" s="3" t="s">
         <v>333</v>
@@ -80125,7 +80137,7 @@
     </row>
     <row r="491" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A491" s="3" t="s">
-        <v>1105</v>
+        <v>1100</v>
       </c>
       <c r="B491" s="3" t="s">
         <v>1068</v>
@@ -80146,10 +80158,10 @@
         <v>7</v>
       </c>
       <c r="H491" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I491" s="4" t="s">
-        <v>16</v>
+        <v>2456</v>
       </c>
       <c r="J491" s="3" t="s">
         <v>333</v>
@@ -80164,7 +80176,7 @@
     </row>
     <row r="492" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A492" s="3" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
       <c r="B492" s="3" t="s">
         <v>1068</v>
@@ -80203,7 +80215,7 @@
     </row>
     <row r="493" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A493" s="3" t="s">
-        <v>1105</v>
+        <v>1100</v>
       </c>
       <c r="B493" s="3" t="s">
         <v>1068</v>
@@ -80263,10 +80275,10 @@
         <v>7</v>
       </c>
       <c r="H494" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I494" s="4" t="s">
-        <v>2459</v>
+        <v>16</v>
       </c>
       <c r="J494" s="3" t="s">
         <v>333</v>
@@ -80302,10 +80314,10 @@
         <v>7</v>
       </c>
       <c r="H495" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I495" s="4" t="s">
-        <v>2460</v>
+        <v>16</v>
       </c>
       <c r="J495" s="3" t="s">
         <v>333</v>
@@ -80632,7 +80644,7 @@
     </row>
     <row r="504" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A504" s="3" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="B504" s="3" t="s">
         <v>1068</v>
@@ -80653,10 +80665,10 @@
         <v>7</v>
       </c>
       <c r="H504" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I504" s="4" t="s">
-        <v>16</v>
+        <v>2469</v>
       </c>
       <c r="J504" s="3" t="s">
         <v>333</v>
@@ -80671,7 +80683,7 @@
     </row>
     <row r="505" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A505" s="3" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="B505" s="3" t="s">
         <v>1068</v>
@@ -80692,10 +80704,10 @@
         <v>7</v>
       </c>
       <c r="H505" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I505" s="4" t="s">
-        <v>16</v>
+        <v>2470</v>
       </c>
       <c r="J505" s="3" t="s">
         <v>333</v>
@@ -80710,7 +80722,7 @@
     </row>
     <row r="506" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A506" s="3" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="B506" s="3" t="s">
         <v>1068</v>
@@ -80749,7 +80761,7 @@
     </row>
     <row r="507" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A507" s="3" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="B507" s="3" t="s">
         <v>1068</v>
@@ -80809,10 +80821,10 @@
         <v>7</v>
       </c>
       <c r="H508" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I508" s="4" t="s">
-        <v>2473</v>
+        <v>16</v>
       </c>
       <c r="J508" s="3" t="s">
         <v>333</v>
@@ -80848,10 +80860,10 @@
         <v>7</v>
       </c>
       <c r="H509" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I509" s="4" t="s">
-        <v>2474</v>
+        <v>16</v>
       </c>
       <c r="J509" s="3" t="s">
         <v>333</v>
@@ -81176,8 +81188,164 @@
         <f>IFERROR(IF(N(L517)=0,"",L517/K517),"")</f>
       </c>
     </row>
+    <row r="518" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A518" s="3" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B518" s="3" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C518" s="3" t="s">
+        <v>2483</v>
+      </c>
+      <c r="D518" s="4" t="s">
+        <v>2483</v>
+      </c>
+      <c r="E518" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="F518" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="G518" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H518" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I518" s="4" t="s">
+        <v>2483</v>
+      </c>
+      <c r="J518" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="K518" s="6">
+        <v>1</v>
+      </c>
+      <c r="L518" s="7"/>
+      <c r="M518" s="8">
+        <f>IFERROR(IF(N(L518)=0,"",L518/K518),"")</f>
+      </c>
+    </row>
+    <row r="519" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A519" s="3" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B519" s="3" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C519" s="3" t="s">
+        <v>2484</v>
+      </c>
+      <c r="D519" s="4" t="s">
+        <v>2484</v>
+      </c>
+      <c r="E519" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="F519" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="G519" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H519" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I519" s="4" t="s">
+        <v>2484</v>
+      </c>
+      <c r="J519" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="K519" s="6">
+        <v>1</v>
+      </c>
+      <c r="L519" s="7"/>
+      <c r="M519" s="8">
+        <f>IFERROR(IF(N(L519)=0,"",L519/K519),"")</f>
+      </c>
+    </row>
+    <row r="520" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A520" s="3" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B520" s="3" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C520" s="3" t="s">
+        <v>2485</v>
+      </c>
+      <c r="D520" s="4" t="s">
+        <v>2485</v>
+      </c>
+      <c r="E520" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="F520" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="G520" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H520" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I520" s="4" t="s">
+        <v>2485</v>
+      </c>
+      <c r="J520" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="K520" s="6">
+        <v>1</v>
+      </c>
+      <c r="L520" s="7"/>
+      <c r="M520" s="8">
+        <f>IFERROR(IF(N(L520)=0,"",L520/K520),"")</f>
+      </c>
+    </row>
+    <row r="521" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A521" s="3" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B521" s="3" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C521" s="3" t="s">
+        <v>2486</v>
+      </c>
+      <c r="D521" s="4" t="s">
+        <v>2486</v>
+      </c>
+      <c r="E521" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="F521" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="G521" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H521" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I521" s="4" t="s">
+        <v>2486</v>
+      </c>
+      <c r="J521" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="K521" s="6">
+        <v>1</v>
+      </c>
+      <c r="L521" s="7"/>
+      <c r="M521" s="8">
+        <f>IFERROR(IF(N(L521)=0,"",L521/K521),"")</f>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:M517"/>
+  <autoFilter ref="A2:M521"/>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
   </mergeCells>
@@ -81197,10 +81365,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>2483</v>
+        <v>2487</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>2484</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -81213,10 +81381,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>2485</v>
+        <v>2489</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -81224,15 +81392,15 @@
         <v>13</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>2487</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>2488</v>
+        <v>2492</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>2489</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -81248,7 +81416,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>2490</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -81256,7 +81424,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>2491</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -81264,7 +81432,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>2492</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -81272,7 +81440,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>2493</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -81285,10 +81453,10 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>2494</v>
+        <v>2498</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>2495</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -81301,26 +81469,26 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>2496</v>
+        <v>2500</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>2497</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>2498</v>
+        <v>2502</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>2499</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>2500</v>
+        <v>2504</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>2501</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -81333,10 +81501,10 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>2502</v>
+        <v>2506</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>2503</v>
+        <v>2507</v>
       </c>
     </row>
   </sheetData>

--- a/pricing/starter-catalog-pricing.xlsx
+++ b/pricing/starter-catalog-pricing.xlsx
@@ -330,31 +330,31 @@
     <t>2-2-2-4 SER AL wire</t>
   </si>
   <si>
-    <t>1/0-3 SER AL</t>
+    <t>1/0-1/0-1/0-2 SER AL</t>
   </si>
   <si>
     <t>1/0</t>
   </si>
   <si>
-    <t>1/0-3 SER AL wire</t>
-  </si>
-  <si>
-    <t>2/0-3 SER AL</t>
+    <t>1/0-1/0-1/0-2 SER AL wire</t>
+  </si>
+  <si>
+    <t>2/0-2/0-2/0-1 SER AL</t>
   </si>
   <si>
     <t>2/0</t>
   </si>
   <si>
-    <t>2/0-3 SER AL wire</t>
-  </si>
-  <si>
-    <t>3/0-3 SER AL</t>
+    <t>2/0-2/0-2/0-1 SER AL wire</t>
+  </si>
+  <si>
+    <t>3/0-3/0-3/0-1/0 SER AL</t>
   </si>
   <si>
     <t>3/0</t>
   </si>
   <si>
-    <t>3/0-3 SER AL wire</t>
+    <t>3/0-3/0-3/0-1/0 SER AL wire</t>
   </si>
   <si>
     <t>4/0-4/0-2/0 SER AL</t>
@@ -378,37 +378,37 @@
     <t>250-250-250 SER AL wire</t>
   </si>
   <si>
-    <t>8-3 SER CU</t>
+    <t>8-8-8-8 SER CU</t>
   </si>
   <si>
     <t>SER CU</t>
   </si>
   <si>
-    <t>8-3 SER CU wire</t>
-  </si>
-  <si>
-    <t>6-3 SER CU</t>
-  </si>
-  <si>
-    <t>6-3 SER CU wire</t>
-  </si>
-  <si>
-    <t>4-3 SER CU</t>
-  </si>
-  <si>
-    <t>4-3 SER CU wire</t>
-  </si>
-  <si>
-    <t>2-3 SER CU</t>
-  </si>
-  <si>
-    <t>2-3 SER CU wire</t>
-  </si>
-  <si>
-    <t>1-3 SER CU</t>
-  </si>
-  <si>
-    <t>1-3 SER CU wire</t>
+    <t>8-8-8-8 SER CU wire</t>
+  </si>
+  <si>
+    <t>6-6-6-6 SER CU</t>
+  </si>
+  <si>
+    <t>6-6-6-6 SER CU wire</t>
+  </si>
+  <si>
+    <t>4-4-4-6 SER CU</t>
+  </si>
+  <si>
+    <t>4-4-4-6 SER CU wire</t>
+  </si>
+  <si>
+    <t>2-2-2-4 SER CU</t>
+  </si>
+  <si>
+    <t>2-2-2-4 SER CU wire</t>
+  </si>
+  <si>
+    <t>1-1-1-3 SER CU</t>
+  </si>
+  <si>
+    <t>1-1-1-3 SER CU wire</t>
   </si>
   <si>
     <t>4-4-6 SEU AL</t>
